--- a/outputs/SA_mlf.xlsx
+++ b/outputs/SA_mlf.xlsx
@@ -2667,8 +2667,10 @@
           <t>MINTNL1</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
-        <v/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>MINTARO</t>
+        </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
@@ -3803,8 +3805,10 @@
           <t>SATGN1</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n">
-        <v/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SATGN</t>
+        </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
@@ -4257,8 +4261,10 @@
           <t>DG_SA1</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
-        <v/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>DG_SA1</t>
+        </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
@@ -4313,8 +4319,10 @@
           <t>TORNL1</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
-        <v/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>TORRIS</t>
+        </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
@@ -4655,8 +4663,10 @@
           <t>DRYCNL</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n">
-        <v/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>DRYCGT</t>
+        </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
@@ -4711,8 +4721,10 @@
           <t>SATGS1</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n">
-        <v/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SATGS</t>
+        </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
@@ -5751,8 +5763,10 @@
           <t>STANV1</t>
         </is>
       </c>
-      <c r="B93" s="2" t="n">
-        <v/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>STANVAC</t>
+        </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
@@ -5781,8 +5795,10 @@
           <t>STANV2</t>
         </is>
       </c>
-      <c r="B94" s="2" t="n">
-        <v/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>STANVAC</t>
+        </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
@@ -5811,8 +5827,10 @@
           <t>TEATREE1</t>
         </is>
       </c>
-      <c r="B95" s="2" t="n">
-        <v/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>TEATREE</t>
+        </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
@@ -5841,8 +5859,10 @@
           <t>HIGHBRY1</t>
         </is>
       </c>
-      <c r="B96" s="2" t="n">
-        <v/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>HIGHBRY</t>
+        </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
@@ -5871,8 +5891,10 @@
           <t>ANGAS2</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n">
-        <v/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>ANGASTON</t>
+        </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
@@ -5901,8 +5923,10 @@
           <t>ANGAS1</t>
         </is>
       </c>
-      <c r="B98" s="2" t="n">
-        <v/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>ANGASTON</t>
+        </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
@@ -5931,8 +5955,10 @@
           <t>AMCORGR</t>
         </is>
       </c>
-      <c r="B99" s="2" t="n">
-        <v/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>AMCORGR</t>
+        </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
@@ -5961,8 +5987,10 @@
           <t>PLAYB-AG</t>
         </is>
       </c>
-      <c r="B100" s="2" t="n">
-        <v/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>PLAYF</t>
+        </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
@@ -5993,8 +6021,10 @@
           <t>NPS1</t>
         </is>
       </c>
-      <c r="B101" s="2" t="n">
-        <v/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>NORTHP</t>
+        </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
@@ -6025,8 +6055,10 @@
           <t>NPS2</t>
         </is>
       </c>
-      <c r="B102" s="2" t="n">
-        <v/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>NORTHP</t>
+        </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
@@ -6057,8 +6089,10 @@
           <t>NPSNL1</t>
         </is>
       </c>
-      <c r="B103" s="2" t="n">
-        <v/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>NORTHP</t>
+        </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
@@ -6089,8 +6123,10 @@
           <t>NPSNL2</t>
         </is>
       </c>
-      <c r="B104" s="2" t="n">
-        <v/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>NORTHP</t>
+        </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
@@ -6121,8 +6157,10 @@
           <t>PEDLER1</t>
         </is>
       </c>
-      <c r="B105" s="2" t="n">
-        <v/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>PEDLER</t>
+        </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
@@ -6155,8 +6193,10 @@
           <t>BLULAKE1</t>
         </is>
       </c>
-      <c r="B106" s="2" t="n">
-        <v/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>BLULAKE</t>
+        </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
@@ -6189,8 +6229,10 @@
           <t>TERMSTOR</t>
         </is>
       </c>
-      <c r="B107" s="2" t="n">
-        <v/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>TERMSTOR</t>
+        </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
@@ -6223,8 +6265,10 @@
           <t>TORRA2</t>
         </is>
       </c>
-      <c r="B108" s="2" t="n">
-        <v/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>TORRIS</t>
+        </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
@@ -6263,8 +6307,10 @@
           <t>TORRA4</t>
         </is>
       </c>
-      <c r="B109" s="2" t="n">
-        <v/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>TORRIS</t>
+        </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
@@ -6303,8 +6349,10 @@
           <t>TORRA1</t>
         </is>
       </c>
-      <c r="B110" s="2" t="n">
-        <v/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>TORRIS</t>
+        </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
@@ -6345,8 +6393,10 @@
           <t>TORRA3</t>
         </is>
       </c>
-      <c r="B111" s="2" t="n">
-        <v/>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>TORRIS</t>
+        </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
@@ -6389,8 +6439,10 @@
           <t>TB2BG1</t>
         </is>
       </c>
-      <c r="B112" s="2" t="n">
-        <v/>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>TB2HYB</t>
+        </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
@@ -6423,8 +6475,10 @@
           <t>LBBG1</t>
         </is>
       </c>
-      <c r="B113" s="2" t="n">
-        <v/>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>LBBESS</t>
+        </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
@@ -6463,8 +6517,10 @@
           <t>HVWWBA1G</t>
         </is>
       </c>
-      <c r="B114" s="2" t="n">
-        <v/>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>HVWW</t>
+        </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
@@ -6499,8 +6555,10 @@
           <t>HPRG1</t>
         </is>
       </c>
-      <c r="B115" s="2" t="n">
-        <v/>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>HORNSDPR</t>
+        </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
@@ -6543,8 +6601,10 @@
           <t>TIBG1</t>
         </is>
       </c>
-      <c r="B116" s="2" t="n">
-        <v/>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>TIBESS</t>
+        </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
@@ -6577,8 +6637,10 @@
           <t>DALNTH01</t>
         </is>
       </c>
-      <c r="B117" s="2" t="n">
-        <v/>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>DALNTH</t>
+        </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
@@ -6621,8 +6683,10 @@
           <t>BOWWBA1G</t>
         </is>
       </c>
-      <c r="B118" s="2" t="n">
-        <v/>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>BOLIVAR</t>
+        </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
@@ -6657,8 +6721,10 @@
           <t>ADPBA1G</t>
         </is>
       </c>
-      <c r="B119" s="2" t="n">
-        <v/>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
@@ -6695,8 +6761,10 @@
           <t>CBWWBA1G</t>
         </is>
       </c>
-      <c r="B120" s="2" t="n">
-        <v/>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>CBWW</t>
+        </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>

--- a/outputs/SA_mlf.xlsx
+++ b/outputs/SA_mlf.xlsx
@@ -2669,13 +2669,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MINTARO</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>Mintaro Gas Turbine Station</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E38" s="4" t="n">
         <v>0.9881</v>
       </c>
@@ -3807,13 +3811,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SATGN</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>Temporary Generation North</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>154</v>
+      </c>
       <c r="E57" s="4" t="inlineStr"/>
       <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
@@ -4263,13 +4271,13 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>DG_SA1</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+          <t>SA1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="3" t="n">
+        <v>3000</v>
+      </c>
       <c r="E65" s="4" t="n">
         <v>1</v>
       </c>
@@ -4321,13 +4329,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>TORRIS</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+          <t>TORRENS ISLAND POWER STATION</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="E66" s="4" t="n">
         <v>1</v>
       </c>
@@ -4665,7 +4677,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>DRYCGT</t>
+          <t>Dry Creek Gas Turbine Station</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -4723,13 +4735,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SATGS</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
+          <t>Temporary Generation South</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>123</v>
+      </c>
       <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
@@ -5765,13 +5781,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>STANVAC</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D93" s="2" t="inlineStr"/>
+          <t>Pt Stanvac Power Station</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>58</v>
+      </c>
       <c r="E93" s="4" t="n">
         <v>1.0075</v>
       </c>
@@ -5797,13 +5817,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>STANVAC</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
+          <t>Pt Stanvac Power Station</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>58</v>
+      </c>
       <c r="E94" s="4" t="n">
         <v>1.0075</v>
       </c>
@@ -5829,13 +5853,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>TEATREE</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D95" s="2" t="inlineStr"/>
+          <t>Tea Tree Gully Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E95" s="4" t="n">
         <v>1.0042</v>
       </c>
@@ -5861,13 +5889,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>HIGHBRY</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
+          <t>Highbury Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="E96" s="4" t="n">
         <v>1.0042</v>
       </c>
@@ -5893,13 +5925,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>ANGASTON</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D97" s="2" t="inlineStr"/>
+          <t>ANGASTON POWER STATION</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>20</v>
+      </c>
       <c r="E97" s="4" t="n">
         <v>1.0061</v>
       </c>
@@ -5925,13 +5961,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>ANGASTON</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
+          <t>ANGASTON POWER STATION</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>30</v>
+      </c>
       <c r="E98" s="4" t="n">
         <v>1.0061</v>
       </c>
@@ -5957,7 +5997,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>AMCORGR</t>
+          <t>Amcor Glass, Gawler Plant</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -5989,7 +6029,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>PLAYF</t>
+          <t>Playford B Power Station</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -6023,13 +6063,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>NORTHP</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D101" s="2" t="inlineStr"/>
+          <t>NORTHERN POWER STATION</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>265</v>
+      </c>
       <c r="E101" s="4" t="n">
         <v>0.9826</v>
       </c>
@@ -6057,13 +6101,17 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>NORTHP</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D102" s="2" t="inlineStr"/>
+          <t>NORTHERN POWER STATION</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>265</v>
+      </c>
       <c r="E102" s="4" t="n">
         <v>0.9826</v>
       </c>
@@ -6091,13 +6139,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>NORTHP</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D103" s="2" t="inlineStr"/>
+          <t>NORTHERN POWER STATION</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="E103" s="4" t="n">
         <v>0.9929</v>
       </c>
@@ -6125,13 +6177,17 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>NORTHP</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D104" s="2" t="inlineStr"/>
+          <t>NORTHERN POWER STATION</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="E104" s="4" t="n">
         <v>1.0482</v>
       </c>
@@ -6159,13 +6215,17 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>PEDLER</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D105" s="2" t="inlineStr"/>
+          <t>Pedler Creek Landfill Gas Power Station Units 1-3</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="E105" s="4" t="n">
         <v>1.0075</v>
       </c>
@@ -6195,13 +6255,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>BLULAKE</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D106" s="2" t="inlineStr"/>
+          <t>Blue Lake Milling Power Plant</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E106" s="4" t="n">
         <v>1.0062</v>
       </c>
@@ -6231,13 +6295,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>TERMSTOR</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D107" s="2" t="inlineStr"/>
+          <t>Terminal Storage Mini Hydro Power Station</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="E107" s="4" t="n">
         <v>1.0042</v>
       </c>
@@ -6267,13 +6335,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>TORRIS</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
+          <t>TORRENS ISLAND POWER STATION</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>120</v>
+      </c>
       <c r="E108" s="4" t="n">
         <v>1.0019</v>
       </c>
@@ -6309,13 +6381,17 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>TORRIS</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D109" s="2" t="inlineStr"/>
+          <t>TORRENS ISLAND POWER STATION</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>120</v>
+      </c>
       <c r="E109" s="4" t="n">
         <v>1.0019</v>
       </c>
@@ -6351,13 +6427,17 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>TORRIS</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D110" s="2" t="inlineStr"/>
+          <t>TORRENS ISLAND POWER STATION</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>120</v>
+      </c>
       <c r="E110" s="4" t="n">
         <v>1.0019</v>
       </c>
@@ -6395,13 +6475,17 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>TORRIS</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D111" s="2" t="inlineStr"/>
+          <t>TORRENS ISLAND POWER STATION</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>120</v>
+      </c>
       <c r="E111" s="4" t="n">
         <v>1.0019</v>
       </c>
@@ -6441,7 +6525,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>TB2HYB</t>
+          <t>Tailem Bend 2 Hybrid Renewable Power Station</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
@@ -6477,13 +6561,17 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>LBBESS</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D113" s="2" t="inlineStr"/>
+          <t>Lake Bonney BESS1</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E113" s="4" t="inlineStr"/>
       <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="inlineStr"/>
@@ -6519,13 +6607,17 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>HVWW</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
+          <t>Happy Valley WTP</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="E114" s="4" t="inlineStr"/>
       <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="inlineStr"/>
@@ -6557,13 +6649,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>HORNSDPR</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="inlineStr"/>
+          <t>Hornsdale Power Reserve</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>150</v>
+      </c>
       <c r="E115" s="4" t="inlineStr"/>
       <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
@@ -6603,13 +6699,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>TIBESS</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="inlineStr"/>
+          <t>Torrens Island BESS</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>250</v>
+      </c>
       <c r="E116" s="4" t="inlineStr"/>
       <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="inlineStr"/>
@@ -6639,13 +6739,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>DALNTH</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="inlineStr"/>
+          <t>Dalrymple North BESS</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>30</v>
+      </c>
       <c r="E117" s="4" t="inlineStr"/>
       <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
@@ -6685,13 +6789,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>BOLIVAR</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D118" s="2" t="inlineStr"/>
+          <t>Bolivar Waste Water Treatment Plant</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="E118" s="4" t="inlineStr"/>
       <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="inlineStr"/>
@@ -6723,13 +6831,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>ADP</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D119" s="2" t="inlineStr"/>
+          <t>Adelaide Desalination Plant</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="inlineStr"/>
@@ -6763,13 +6875,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>CBWW</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D120" s="2" t="inlineStr"/>
+          <t>Christies Beach WWTP</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="E120" s="4" t="inlineStr"/>
       <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="inlineStr"/>

--- a/outputs/SA_mlf.xlsx
+++ b/outputs/SA_mlf.xlsx
@@ -719,13 +719,21 @@
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="n">
+        <v>0.9005</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0.9337</v>
+      </c>
       <c r="P4" s="4" t="n">
         <v>0.9358</v>
       </c>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
+      <c r="Q4" s="4" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -916,12 +924,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Lake Bonney Wind Farm Stage 1</t>
+          <t>Lake Bonney Stage 2 Windfarm</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -930,7 +938,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>80.5</v>
+        <v>159</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0.9352</v>
@@ -978,12 +986,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LKBONNY2</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 2 Windfarm</t>
+          <t>Lake Bonney Wind Farm Stage 1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -992,7 +1000,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>159</v>
+        <v>80.5</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0.9352</v>
@@ -1102,12 +1110,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HDWF1</t>
+          <t>HDWF3</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm</t>
+          <t>Hornsdale Wind Farm 3</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1116,16 +1124,12 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0.9792999999999999</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0.9965000000000001</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
-        <v>0.9841</v>
+        <v>0.9799</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>0.9744</v>
@@ -1224,12 +1228,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HDWF3</t>
+          <t>HDWF1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 3</t>
+          <t>Hornsdale Wind Farm</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1238,12 +1242,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+        <v>102.4</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.9965000000000001</v>
+      </c>
       <c r="G13" s="4" t="n">
-        <v>0.9799</v>
+        <v>0.9841</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>0.9744</v>
@@ -1334,12 +1342,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>NBHWF1</t>
+          <t>BLUFF1</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>North Brown Hill Wind Farm</t>
+          <t>The Bluff Wind Farm</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1348,7 +1356,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>132.3</v>
+        <v>52.5</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0.9767</v>
@@ -1396,12 +1404,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BLUFF1</t>
+          <t>NBHWF1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>The Bluff Wind Farm</t>
+          <t>North Brown Hill Wind Farm</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1410,7 +1418,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>52.5</v>
+        <v>132.3</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0.9767</v>
@@ -1458,7 +1466,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SNUG3</t>
+          <t>SNUG2</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1520,7 +1528,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SNUG2</t>
+          <t>SNUG3</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2092,12 +2100,18 @@
       <c r="L27" s="4" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr"/>
       <c r="N27" s="4" t="inlineStr"/>
-      <c r="O27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="n">
+        <v>0.9689</v>
+      </c>
       <c r="P27" s="4" t="n">
         <v>0.9661</v>
       </c>
-      <c r="Q27" s="4" t="inlineStr"/>
-      <c r="R27" s="5" t="inlineStr"/>
+      <c r="Q27" s="4" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>-0.29</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2296,12 +2310,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Snowtown Wind Farm Stage 2 North</t>
+          <t>Snowtown South Wind Farm</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2310,7 +2324,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>0.9782</v>
@@ -2358,12 +2372,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Snowtown South Wind Farm</t>
+          <t>Snowtown Wind Farm Stage 2 North</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2372,7 +2386,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>0.9782</v>
@@ -2534,7 +2548,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PAREPS1</t>
+          <t>PAREPW1</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2544,11 +2558,11 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>99</v>
+        <v>210</v>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr"/>
@@ -2556,7 +2570,9 @@
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr"/>
-      <c r="K36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="n">
+        <v>0.9728</v>
+      </c>
       <c r="L36" s="4" t="n">
         <v>0.9641</v>
       </c>
@@ -2582,7 +2598,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PAREPW1</t>
+          <t>PAREPS1</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2592,11 +2608,11 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>210</v>
+        <v>99</v>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr"/>
@@ -2604,9 +2620,7 @@
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr"/>
-      <c r="K37" s="4" t="n">
-        <v>0.9728</v>
-      </c>
+      <c r="K37" s="4" t="inlineStr"/>
       <c r="L37" s="4" t="n">
         <v>0.9641</v>
       </c>
@@ -2709,13 +2723,21 @@
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr"/>
       <c r="M39" s="4" t="inlineStr"/>
-      <c r="N39" s="4" t="inlineStr"/>
-      <c r="O39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0.9806</v>
+      </c>
       <c r="P39" s="4" t="n">
         <v>0.975</v>
       </c>
-      <c r="Q39" s="4" t="inlineStr"/>
-      <c r="R39" s="5" t="inlineStr"/>
+      <c r="Q39" s="4" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>-0.57</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2958,7 +2980,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3020,7 +3042,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3144,7 +3166,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>QPS2</t>
+          <t>QPS5</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3158,7 +3180,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>0.9932</v>
@@ -3206,7 +3228,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>QPS1</t>
+          <t>QPS4</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3220,7 +3242,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E48" s="4" t="n">
         <v>0.9932</v>
@@ -3268,7 +3290,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>QPS4</t>
+          <t>QPS3</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3330,7 +3352,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>QPS3</t>
+          <t>QPS2</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3392,7 +3414,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>QPS5</t>
+          <t>QPS1</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3406,7 +3428,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>0.9932</v>
@@ -3562,7 +3584,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3572,11 +3594,11 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr"/>
@@ -3585,20 +3607,32 @@
       <c r="I54" s="4" t="inlineStr"/>
       <c r="J54" s="4" t="inlineStr"/>
       <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr"/>
-      <c r="M54" s="4" t="inlineStr"/>
-      <c r="N54" s="4" t="inlineStr"/>
-      <c r="O54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="n">
+        <v>0.9687</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>1.0079</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>1.0102</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="P54" s="4" t="n">
         <v>0.9968</v>
       </c>
-      <c r="Q54" s="4" t="inlineStr"/>
-      <c r="R54" s="5" t="inlineStr"/>
+      <c r="Q54" s="4" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>0.23</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3608,11 +3642,11 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="4" t="inlineStr"/>
@@ -3621,12 +3655,8 @@
       <c r="I55" s="4" t="inlineStr"/>
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="n">
-        <v>0.9687</v>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>1.0079</v>
-      </c>
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr"/>
       <c r="N55" s="4" t="n">
         <v>1.0102</v>
       </c>
@@ -3702,7 +3732,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DRYCGT1</t>
+          <t>DRYCGT3</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3764,7 +3794,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>DRYCGT3</t>
+          <t>DRYCGT2</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3826,7 +3856,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>DRYCGT2</t>
+          <t>DRYCGT1</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -4022,12 +4052,18 @@
       <c r="L62" s="4" t="inlineStr"/>
       <c r="M62" s="4" t="inlineStr"/>
       <c r="N62" s="4" t="inlineStr"/>
-      <c r="O62" s="4" t="inlineStr"/>
+      <c r="O62" s="4" t="n">
+        <v>0.9984</v>
+      </c>
       <c r="P62" s="4" t="n">
         <v>0.9994</v>
       </c>
-      <c r="Q62" s="4" t="inlineStr"/>
-      <c r="R62" s="5" t="inlineStr"/>
+      <c r="Q62" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="R62" s="5" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4057,18 +4093,26 @@
       <c r="K63" s="4" t="inlineStr"/>
       <c r="L63" s="4" t="inlineStr"/>
       <c r="M63" s="4" t="inlineStr"/>
-      <c r="N63" s="4" t="inlineStr"/>
-      <c r="O63" s="4" t="inlineStr"/>
+      <c r="N63" s="4" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="O63" s="4" t="n">
+        <v>0.9993</v>
+      </c>
       <c r="P63" s="4" t="n">
         <v>0.9994</v>
       </c>
-      <c r="Q63" s="4" t="inlineStr"/>
-      <c r="R63" s="5" t="inlineStr"/>
+      <c r="Q63" s="4" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="R63" s="5" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TORRB4</t>
+          <t>TORRB3</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4130,7 +4174,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TORRB3</t>
+          <t>TORRB4</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4482,17 +4526,21 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>DG_SA1</t>
+          <t>TORNL1</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SA1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr"/>
+          <t>TORRENS ISLAND POWER STATION</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D71" s="3" t="n">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="E71" s="4" t="n">
         <v>1</v>
@@ -4540,21 +4588,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>TORNL1</t>
+          <t>DG_SA1</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>TORRENS ISLAND POWER STATION</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+          <t>SA1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="3" t="n">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="E72" s="4" t="n">
         <v>1</v>
@@ -4602,7 +4646,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>BOWWPV1</t>
+          <t>BOWWBA1</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4612,11 +4656,11 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>8.25</v>
+        <v>3</v>
       </c>
       <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr"/>
@@ -4624,15 +4668,9 @@
       <c r="H73" s="4" t="inlineStr"/>
       <c r="I73" s="4" t="inlineStr"/>
       <c r="J73" s="4" t="inlineStr"/>
-      <c r="K73" s="4" t="n">
-        <v>1.0011</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>1.0002</v>
-      </c>
-      <c r="M73" s="4" t="n">
-        <v>0.9995000000000001</v>
-      </c>
+      <c r="K73" s="4" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr"/>
+      <c r="M73" s="4" t="inlineStr"/>
       <c r="N73" s="4" t="n">
         <v>1.0004</v>
       </c>
@@ -4652,7 +4690,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>BOLIVAR1</t>
+          <t>BOWWDG1</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4662,30 +4700,18 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="F74" s="4" t="n">
-        <v>1.0054</v>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="H74" s="4" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="I74" s="4" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="J74" s="4" t="n">
-        <v>1.0012</v>
-      </c>
+        <v>0.66</v>
+      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr"/>
+      <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr"/>
+      <c r="J74" s="4" t="inlineStr"/>
       <c r="K74" s="4" t="n">
         <v>1.0011</v>
       </c>
@@ -4714,7 +4740,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>BOWWDG1</t>
+          <t>BOLIVAR1</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4724,18 +4750,30 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
-      <c r="G75" s="4" t="inlineStr"/>
-      <c r="H75" s="4" t="inlineStr"/>
-      <c r="I75" s="4" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr"/>
+        <v>9.9</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>1.0045</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="J75" s="4" t="n">
+        <v>1.0012</v>
+      </c>
       <c r="K75" s="4" t="n">
         <v>1.0011</v>
       </c>
@@ -4764,7 +4802,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>BOWWBA1</t>
+          <t>BOWWPV1</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4774,11 +4812,11 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>3</v>
+        <v>8.25</v>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr"/>
@@ -4786,16 +4824,30 @@
       <c r="H76" s="4" t="inlineStr"/>
       <c r="I76" s="4" t="inlineStr"/>
       <c r="J76" s="4" t="inlineStr"/>
-      <c r="K76" s="4" t="inlineStr"/>
-      <c r="L76" s="4" t="inlineStr"/>
-      <c r="M76" s="4" t="inlineStr"/>
-      <c r="N76" s="4" t="inlineStr"/>
-      <c r="O76" s="4" t="inlineStr"/>
+      <c r="K76" s="4" t="n">
+        <v>1.0011</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="M76" s="4" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>1.0004</v>
+      </c>
+      <c r="O76" s="4" t="n">
+        <v>0.9999</v>
+      </c>
       <c r="P76" s="4" t="n">
         <v>1.0002</v>
       </c>
-      <c r="Q76" s="4" t="inlineStr"/>
-      <c r="R76" s="5" t="inlineStr"/>
+      <c r="Q76" s="4" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="R76" s="5" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5151,13 +5203,21 @@
       <c r="K83" s="4" t="inlineStr"/>
       <c r="L83" s="4" t="inlineStr"/>
       <c r="M83" s="4" t="inlineStr"/>
-      <c r="N83" s="4" t="inlineStr"/>
-      <c r="O83" s="4" t="inlineStr"/>
+      <c r="N83" s="4" t="n">
+        <v>1.0043</v>
+      </c>
+      <c r="O83" s="4" t="n">
+        <v>1.0024</v>
+      </c>
       <c r="P83" s="4" t="n">
         <v>1.0022</v>
       </c>
-      <c r="Q83" s="4" t="inlineStr"/>
-      <c r="R83" s="5" t="inlineStr"/>
+      <c r="Q83" s="4" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="R83" s="5" t="n">
+        <v>-0.02</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5224,101 +5284,167 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>CBWWBA1</t>
+          <t>PTSTAN1</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Pt Stanvac Power Station</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr"/>
-      <c r="H85" s="4" t="inlineStr"/>
-      <c r="I85" s="4" t="inlineStr"/>
-      <c r="J85" s="4" t="inlineStr"/>
-      <c r="K85" s="4" t="inlineStr"/>
-      <c r="L85" s="4" t="inlineStr"/>
-      <c r="M85" s="4" t="inlineStr"/>
-      <c r="N85" s="4" t="inlineStr"/>
-      <c r="O85" s="4" t="inlineStr"/>
+        <v>57.6</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J85" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="K85" s="4" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="L85" s="4" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="M85" s="4" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="N85" s="4" t="n">
+        <v>1.0025</v>
+      </c>
+      <c r="O85" s="4" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="P85" s="4" t="n">
         <v>1.0033</v>
       </c>
-      <c r="Q85" s="4" t="inlineStr"/>
-      <c r="R85" s="5" t="inlineStr"/>
+      <c r="Q85" s="4" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="R85" s="5" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ADPBA1</t>
+          <t>STARHLWF</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Starfish Hill Wind Farm</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="4" t="inlineStr"/>
-      <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="4" t="inlineStr"/>
-      <c r="J86" s="4" t="inlineStr"/>
-      <c r="K86" s="4" t="inlineStr"/>
-      <c r="L86" s="4" t="inlineStr"/>
-      <c r="M86" s="4" t="inlineStr"/>
-      <c r="N86" s="4" t="inlineStr"/>
-      <c r="O86" s="4" t="inlineStr"/>
+        <v>34.5</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="K86" s="4" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="M86" s="4" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="N86" s="4" t="n">
+        <v>1.0025</v>
+      </c>
+      <c r="O86" s="4" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="P86" s="4" t="n">
         <v>1.0033</v>
       </c>
-      <c r="Q86" s="4" t="inlineStr"/>
-      <c r="R86" s="5" t="inlineStr"/>
+      <c r="Q86" s="4" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="R86" s="5" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>CBWWPV2</t>
+          <t>LONSDALE</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Lonsdale Power Station</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr"/>
-      <c r="H87" s="4" t="inlineStr"/>
-      <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="4" t="inlineStr"/>
-      <c r="K87" s="4" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J87" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="K87" s="4" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L87" s="4" t="n">
         <v>1.0036</v>
       </c>
@@ -5344,7 +5470,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>CBWWPV1</t>
+          <t>CBWWBA1</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5354,11 +5480,11 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
       <c r="F88" s="4" t="inlineStr"/>
@@ -5367,12 +5493,8 @@
       <c r="I88" s="4" t="inlineStr"/>
       <c r="J88" s="4" t="inlineStr"/>
       <c r="K88" s="4" t="inlineStr"/>
-      <c r="L88" s="4" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="M88" s="4" t="n">
-        <v>1.0039</v>
-      </c>
+      <c r="L88" s="4" t="inlineStr"/>
+      <c r="M88" s="4" t="inlineStr"/>
       <c r="N88" s="4" t="n">
         <v>1.0025</v>
       </c>
@@ -5392,43 +5514,29 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>LONSDALE</t>
+          <t>CBWWPV1</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Lonsdale Power Station</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F89" s="4" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G89" s="4" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H89" s="4" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I89" s="4" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="J89" s="4" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="K89" s="4" t="n">
-        <v>1.0055</v>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr"/>
+      <c r="J89" s="4" t="inlineStr"/>
+      <c r="K89" s="4" t="inlineStr"/>
       <c r="L89" s="4" t="n">
         <v>1.0036</v>
       </c>
@@ -5454,7 +5562,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>CBWWBG1</t>
+          <t>CBWWPV2</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5464,11 +5572,11 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.664</v>
+        <v>1.08</v>
       </c>
       <c r="E90" s="4" t="inlineStr"/>
       <c r="F90" s="4" t="inlineStr"/>
@@ -5502,43 +5610,29 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
+          <t>CBWWDG2</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Starfish Hill Wind Farm</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E91" s="4" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F91" s="4" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G91" s="4" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H91" s="4" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I91" s="4" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="J91" s="4" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="K91" s="4" t="n">
-        <v>1.0055</v>
-      </c>
+        <v>0.72</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr"/>
       <c r="L91" s="4" t="n">
         <v>1.0036</v>
       </c>
@@ -5564,7 +5658,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>CBWWDG2</t>
+          <t>CBWWDG1</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5578,7 +5672,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.72</v>
+        <v>2</v>
       </c>
       <c r="E92" s="4" t="inlineStr"/>
       <c r="F92" s="4" t="inlineStr"/>
@@ -5612,7 +5706,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ADPPV2</t>
+          <t>ADPPV3</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5626,7 +5720,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="E93" s="4" t="inlineStr"/>
       <c r="F93" s="4" t="inlineStr"/>
@@ -5662,7 +5756,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ADPPV3</t>
+          <t>ADPPV2</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5676,7 +5770,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="E94" s="4" t="inlineStr"/>
       <c r="F94" s="4" t="inlineStr"/>
@@ -5764,49 +5858,31 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>PTSTAN1</t>
+          <t>ADPBA1</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Pt Stanvac Power Station</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="E96" s="4" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F96" s="4" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I96" s="4" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="K96" s="4" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="L96" s="4" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="M96" s="4" t="n">
-        <v>1.0039</v>
-      </c>
+        <v>7.76</v>
+      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr"/>
+      <c r="K96" s="4" t="inlineStr"/>
+      <c r="L96" s="4" t="inlineStr"/>
+      <c r="M96" s="4" t="inlineStr"/>
       <c r="N96" s="4" t="n">
         <v>1.0025</v>
       </c>
@@ -5876,7 +5952,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>CBWWDG1</t>
+          <t>CBWWBG1</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5886,11 +5962,11 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>2</v>
+        <v>0.664</v>
       </c>
       <c r="E98" s="4" t="inlineStr"/>
       <c r="F98" s="4" t="inlineStr"/>
@@ -5949,13 +6025,21 @@
       <c r="K99" s="4" t="inlineStr"/>
       <c r="L99" s="4" t="inlineStr"/>
       <c r="M99" s="4" t="inlineStr"/>
-      <c r="N99" s="4" t="inlineStr"/>
-      <c r="O99" s="4" t="inlineStr"/>
+      <c r="N99" s="4" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="O99" s="4" t="n">
+        <v>1.0072</v>
+      </c>
       <c r="P99" s="4" t="n">
         <v>1.0047</v>
       </c>
-      <c r="Q99" s="4" t="inlineStr"/>
-      <c r="R99" s="5" t="inlineStr"/>
+      <c r="Q99" s="4" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="R99" s="5" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5985,13 +6069,21 @@
       <c r="K100" s="4" t="inlineStr"/>
       <c r="L100" s="4" t="inlineStr"/>
       <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr"/>
-      <c r="O100" s="4" t="inlineStr"/>
+      <c r="N100" s="4" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="O100" s="4" t="n">
+        <v>0.9905</v>
+      </c>
       <c r="P100" s="4" t="n">
         <v>1.0056</v>
       </c>
-      <c r="Q100" s="4" t="inlineStr"/>
-      <c r="R100" s="5" t="inlineStr"/>
+      <c r="Q100" s="4" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="R100" s="5" t="n">
+        <v>1.52</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6083,13 +6175,21 @@
       <c r="K102" s="4" t="inlineStr"/>
       <c r="L102" s="4" t="inlineStr"/>
       <c r="M102" s="4" t="inlineStr"/>
-      <c r="N102" s="4" t="inlineStr"/>
-      <c r="O102" s="4" t="inlineStr"/>
+      <c r="N102" s="4" t="n">
+        <v>1.0144</v>
+      </c>
+      <c r="O102" s="4" t="n">
+        <v>1.0294</v>
+      </c>
       <c r="P102" s="4" t="n">
         <v>1.0083</v>
       </c>
-      <c r="Q102" s="4" t="inlineStr"/>
-      <c r="R102" s="5" t="inlineStr"/>
+      <c r="Q102" s="4" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="R102" s="5" t="n">
+        <v>-2.05</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6169,13 +6269,21 @@
       <c r="K104" s="4" t="inlineStr"/>
       <c r="L104" s="4" t="inlineStr"/>
       <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr"/>
-      <c r="O104" s="4" t="inlineStr"/>
+      <c r="N104" s="4" t="n">
+        <v>0.9964</v>
+      </c>
+      <c r="O104" s="4" t="n">
+        <v>1.0146</v>
+      </c>
       <c r="P104" s="4" t="n">
         <v>1.0112</v>
       </c>
-      <c r="Q104" s="4" t="inlineStr"/>
-      <c r="R104" s="5" t="inlineStr"/>
+      <c r="Q104" s="4" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="R104" s="5" t="n">
+        <v>-0.34</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6306,34 +6414,40 @@
       <c r="L107" s="4" t="inlineStr"/>
       <c r="M107" s="4" t="inlineStr"/>
       <c r="N107" s="4" t="inlineStr"/>
-      <c r="O107" s="4" t="inlineStr"/>
+      <c r="O107" s="4" t="n">
+        <v>0.9992</v>
+      </c>
       <c r="P107" s="4" t="n">
         <v>1.0164</v>
       </c>
-      <c r="Q107" s="4" t="inlineStr"/>
-      <c r="R107" s="5" t="inlineStr"/>
+      <c r="Q107" s="4" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="R107" s="5" t="n">
+        <v>1.72</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>STANV1</t>
+          <t>HIGHBRY1</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Pt Stanvac Power Station</t>
+          <t>Highbury Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="F108" s="4" t="inlineStr"/>
       <c r="G108" s="4" t="inlineStr"/>
@@ -6388,24 +6502,24 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TEATREE1</t>
+          <t>STANV1</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Tea Tree Gully Landfill Gas Power Station</t>
+          <t>Pt Stanvac Power Station</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="inlineStr"/>
@@ -6424,24 +6538,24 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>HIGHBRY1</t>
+          <t>ANGAS1</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Highbury Landfill Gas Power Station</t>
+          <t>ANGASTON POWER STATION</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>1.0042</v>
+        <v>1.0061</v>
       </c>
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="inlineStr"/>
@@ -6460,24 +6574,20 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ANGAS2</t>
+          <t>AMCORGR</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>ANGASTON POWER STATION</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="n">
-        <v>20</v>
-      </c>
+          <t>Amcor Glass, Gawler Plant</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="4" t="n">
-        <v>1.0061</v>
+        <v>1.0111</v>
       </c>
       <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="inlineStr"/>
@@ -6496,7 +6606,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ANGAS1</t>
+          <t>ANGAS2</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -6510,7 +6620,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E113" s="4" t="n">
         <v>1.0061</v>
@@ -6532,20 +6642,24 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>AMCORGR</t>
+          <t>TEATREE1</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Amcor Glass, Gawler Plant</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="inlineStr"/>
+          <t>Tea Tree Gully Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E114" s="4" t="n">
-        <v>1.0111</v>
+        <v>1.0042</v>
       </c>
       <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="inlineStr"/>
@@ -6598,7 +6712,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>NPS1</t>
+          <t>NPSNL2</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -6612,13 +6726,13 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>0.9826</v>
+        <v>1.0482</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1.0098</v>
+        <v>1.0791</v>
       </c>
       <c r="G116" s="4" t="inlineStr"/>
       <c r="H116" s="4" t="inlineStr"/>
@@ -6636,7 +6750,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>NPS2</t>
+          <t>NPSNL1</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -6650,13 +6764,13 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>0.9826</v>
+        <v>0.9929</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1.0098</v>
+        <v>1.0132</v>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
       <c r="H117" s="4" t="inlineStr"/>
@@ -6674,7 +6788,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>NPSNL1</t>
+          <t>NPS2</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -6688,13 +6802,13 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>0.9929</v>
+        <v>0.9826</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1.0132</v>
+        <v>1.0098</v>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
       <c r="H118" s="4" t="inlineStr"/>
@@ -6712,7 +6826,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>NPSNL2</t>
+          <t>NPS1</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6726,13 +6840,13 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>1.0482</v>
+        <v>0.9826</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1.0791</v>
+        <v>1.0098</v>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
       <c r="H119" s="4" t="inlineStr"/>
@@ -6750,30 +6864,30 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PEDLER1</t>
+          <t>BLULAKE1</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Pedler Creek Landfill Gas Power Station Units 1-3</t>
+          <t>Blue Lake Milling Power Plant</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>1.0075</v>
+        <v>1.0062</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1.0051</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>1.0047</v>
+        <v>0.978</v>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
       <c r="I120" s="4" t="inlineStr"/>
@@ -6790,30 +6904,30 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>BLULAKE1</t>
+          <t>PEDLER1</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Blue Lake Milling Power Plant</t>
+          <t>Pedler Creek Landfill Gas Power Station Units 1-3</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>1.0062</v>
+        <v>1.0075</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>0.9703000000000001</v>
+        <v>1.0051</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>0.978</v>
+        <v>1.0047</v>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
       <c r="I121" s="4" t="inlineStr"/>
@@ -6870,7 +6984,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>TORRA2</t>
+          <t>TORRA4</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6916,7 +7030,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>TORRA4</t>
+          <t>TORRA2</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -7096,12 +7210,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>LBBG1</t>
+          <t>TIBG1</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Lake Bonney BESS1</t>
+          <t>Torrens Island BESS</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -7110,29 +7224,23 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="inlineStr"/>
       <c r="H128" s="4" t="inlineStr"/>
-      <c r="I128" s="4" t="n">
-        <v>0.9922</v>
-      </c>
-      <c r="J128" s="4" t="n">
-        <v>0.9741</v>
-      </c>
-      <c r="K128" s="4" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="I128" s="4" t="inlineStr"/>
+      <c r="J128" s="4" t="inlineStr"/>
+      <c r="K128" s="4" t="inlineStr"/>
       <c r="L128" s="4" t="n">
-        <v>0.9851</v>
+        <v>1.0001</v>
       </c>
       <c r="M128" s="4" t="n">
-        <v>0.979</v>
+        <v>0.9996</v>
       </c>
       <c r="N128" s="4" t="n">
-        <v>0.9841</v>
+        <v>0.9998</v>
       </c>
       <c r="O128" s="4" t="inlineStr"/>
       <c r="P128" s="4" t="inlineStr"/>
@@ -7142,12 +7250,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>HVWWBA1G</t>
+          <t>BOWWBA1G</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Happy Valley WTP</t>
+          <t>Bolivar Waste Water Treatment Plant</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -7156,7 +7264,7 @@
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E129" s="4" t="inlineStr"/>
       <c r="F129" s="4" t="inlineStr"/>
@@ -7165,16 +7273,16 @@
       <c r="I129" s="4" t="inlineStr"/>
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="n">
-        <v>1.0052</v>
+        <v>1.0011</v>
       </c>
       <c r="L129" s="4" t="n">
-        <v>1.003</v>
+        <v>1.0002</v>
       </c>
       <c r="M129" s="4" t="n">
-        <v>1.0041</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="N129" s="4" t="n">
-        <v>1.0043</v>
+        <v>1.0004</v>
       </c>
       <c r="O129" s="4" t="inlineStr"/>
       <c r="P129" s="4" t="inlineStr"/>
@@ -7184,12 +7292,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>HPRG1</t>
+          <t>LBBG1</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Hornsdale Power Reserve</t>
+          <t>Lake Bonney BESS1</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7198,33 +7306,29 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="E130" s="4" t="inlineStr"/>
       <c r="F130" s="4" t="inlineStr"/>
-      <c r="G130" s="4" t="n">
-        <v>0.9848</v>
-      </c>
-      <c r="H130" s="4" t="n">
-        <v>0.9771</v>
-      </c>
+      <c r="G130" s="4" t="inlineStr"/>
+      <c r="H130" s="4" t="inlineStr"/>
       <c r="I130" s="4" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="J130" s="4" t="n">
+        <v>0.9741</v>
+      </c>
+      <c r="K130" s="4" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="L130" s="4" t="n">
         <v>0.9851</v>
       </c>
-      <c r="J130" s="4" t="n">
-        <v>0.9838</v>
-      </c>
-      <c r="K130" s="4" t="n">
-        <v>0.9772</v>
-      </c>
-      <c r="L130" s="4" t="n">
-        <v>0.9651999999999999</v>
-      </c>
       <c r="M130" s="4" t="n">
-        <v>0.9653</v>
+        <v>0.979</v>
       </c>
       <c r="N130" s="4" t="n">
-        <v>0.9657</v>
+        <v>0.9841</v>
       </c>
       <c r="O130" s="4" t="inlineStr"/>
       <c r="P130" s="4" t="inlineStr"/>
@@ -7234,12 +7338,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TIBG1</t>
+          <t>HVWWBA1G</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Torrens Island BESS</t>
+          <t>Happy Valley WTP</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7248,7 +7352,7 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="4" t="inlineStr"/>
@@ -7256,15 +7360,17 @@
       <c r="H131" s="4" t="inlineStr"/>
       <c r="I131" s="4" t="inlineStr"/>
       <c r="J131" s="4" t="inlineStr"/>
-      <c r="K131" s="4" t="inlineStr"/>
+      <c r="K131" s="4" t="n">
+        <v>1.0052</v>
+      </c>
       <c r="L131" s="4" t="n">
-        <v>1.0001</v>
+        <v>1.003</v>
       </c>
       <c r="M131" s="4" t="n">
-        <v>0.9996</v>
+        <v>1.0041</v>
       </c>
       <c r="N131" s="4" t="n">
-        <v>0.9998</v>
+        <v>1.0043</v>
       </c>
       <c r="O131" s="4" t="inlineStr"/>
       <c r="P131" s="4" t="inlineStr"/>
@@ -7274,12 +7380,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>DALNTH01</t>
+          <t>CBWWBA1G</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Dalrymple North BESS</t>
+          <t>Christies Beach WWTP</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7288,33 +7394,23 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E132" s="4" t="inlineStr"/>
       <c r="F132" s="4" t="inlineStr"/>
-      <c r="G132" s="4" t="n">
-        <v>0.8848</v>
-      </c>
-      <c r="H132" s="4" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="I132" s="4" t="n">
-        <v>0.9045</v>
-      </c>
-      <c r="J132" s="4" t="n">
-        <v>0.9193</v>
-      </c>
-      <c r="K132" s="4" t="n">
-        <v>0.9212</v>
-      </c>
+      <c r="G132" s="4" t="inlineStr"/>
+      <c r="H132" s="4" t="inlineStr"/>
+      <c r="I132" s="4" t="inlineStr"/>
+      <c r="J132" s="4" t="inlineStr"/>
+      <c r="K132" s="4" t="inlineStr"/>
       <c r="L132" s="4" t="n">
-        <v>0.9432</v>
+        <v>1.0036</v>
       </c>
       <c r="M132" s="4" t="n">
-        <v>0.8954</v>
+        <v>1.0039</v>
       </c>
       <c r="N132" s="4" t="n">
-        <v>0.9092</v>
+        <v>1.0025</v>
       </c>
       <c r="O132" s="4" t="inlineStr"/>
       <c r="P132" s="4" t="inlineStr"/>
@@ -7324,12 +7420,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>BOWWBA1G</t>
+          <t>HPRG1</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Bolivar Waste Water Treatment Plant</t>
+          <t>Hornsdale Power Reserve</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7338,25 +7434,33 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="E133" s="4" t="inlineStr"/>
       <c r="F133" s="4" t="inlineStr"/>
-      <c r="G133" s="4" t="inlineStr"/>
-      <c r="H133" s="4" t="inlineStr"/>
-      <c r="I133" s="4" t="inlineStr"/>
-      <c r="J133" s="4" t="inlineStr"/>
+      <c r="G133" s="4" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="H133" s="4" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="I133" s="4" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="J133" s="4" t="n">
+        <v>0.9838</v>
+      </c>
       <c r="K133" s="4" t="n">
-        <v>1.0011</v>
+        <v>0.9772</v>
       </c>
       <c r="L133" s="4" t="n">
-        <v>1.0002</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="M133" s="4" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9653</v>
       </c>
       <c r="N133" s="4" t="n">
-        <v>1.0004</v>
+        <v>0.9657</v>
       </c>
       <c r="O133" s="4" t="inlineStr"/>
       <c r="P133" s="4" t="inlineStr"/>
@@ -7366,12 +7470,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>ADPBA1G</t>
+          <t>DALNTH01</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Dalrymple North BESS</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7380,27 +7484,33 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E134" s="4" t="inlineStr"/>
       <c r="F134" s="4" t="inlineStr"/>
-      <c r="G134" s="4" t="inlineStr"/>
-      <c r="H134" s="4" t="inlineStr"/>
-      <c r="I134" s="4" t="inlineStr"/>
+      <c r="G134" s="4" t="n">
+        <v>0.8848</v>
+      </c>
+      <c r="H134" s="4" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="I134" s="4" t="n">
+        <v>0.9045</v>
+      </c>
       <c r="J134" s="4" t="n">
-        <v>1.0038</v>
+        <v>0.9193</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1.0055</v>
+        <v>0.9212</v>
       </c>
       <c r="L134" s="4" t="n">
-        <v>1.0036</v>
+        <v>0.9432</v>
       </c>
       <c r="M134" s="4" t="n">
-        <v>1.0039</v>
+        <v>0.8954</v>
       </c>
       <c r="N134" s="4" t="n">
-        <v>1.0025</v>
+        <v>0.9092</v>
       </c>
       <c r="O134" s="4" t="inlineStr"/>
       <c r="P134" s="4" t="inlineStr"/>
@@ -7410,12 +7520,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>CBWWBA1G</t>
+          <t>ADPBA1G</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Christies Beach WWTP</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7424,15 +7534,19 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E135" s="4" t="inlineStr"/>
       <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="inlineStr"/>
       <c r="H135" s="4" t="inlineStr"/>
       <c r="I135" s="4" t="inlineStr"/>
-      <c r="J135" s="4" t="inlineStr"/>
-      <c r="K135" s="4" t="inlineStr"/>
+      <c r="J135" s="4" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="K135" s="4" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L135" s="4" t="n">
         <v>1.0036</v>
       </c>
@@ -7644,8 +7758,12 @@
       <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="n">
+        <v>0.9005</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0.9337</v>
+      </c>
       <c r="M4" s="4" t="n">
         <v>0.9358</v>
       </c>
@@ -7782,7 +7900,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY2</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -7825,7 +7943,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LKBONNY2</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -7911,17 +8029,13 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HDWF1</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>0.9792999999999999</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0.9965000000000001</v>
-      </c>
+          <t>HDWF3</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="n">
-        <v>0.9841</v>
+        <v>0.9799</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0.9744</v>
@@ -7995,13 +8109,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HDWF3</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr"/>
+          <t>HDWF1</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0.9965000000000001</v>
+      </c>
       <c r="D13" s="4" t="n">
-        <v>0.9799</v>
+        <v>0.9841</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0.9744</v>
@@ -8067,7 +8185,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>NBHWF1</t>
+          <t>BLUFF1</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -8110,7 +8228,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BLUFF1</t>
+          <t>NBHWF1</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -8153,7 +8271,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SNUG3</t>
+          <t>SNUG2</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -8196,7 +8314,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SNUG2</t>
+          <t>SNUG3</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -8584,7 +8702,9 @@
       <c r="I27" s="4" t="inlineStr"/>
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="n">
+        <v>0.9689</v>
+      </c>
       <c r="M27" s="4" t="n">
         <v>0.9661</v>
       </c>
@@ -8710,7 +8830,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
@@ -8753,7 +8873,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
@@ -8872,7 +8992,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PAREPS1</t>
+          <t>PAREPW1</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr"/>
@@ -8881,7 +9001,9 @@
       <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="n">
+        <v>0.9728</v>
+      </c>
       <c r="I36" s="4" t="n">
         <v>0.9641</v>
       </c>
@@ -8901,7 +9023,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PAREPW1</t>
+          <t>PAREPS1</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr"/>
@@ -8910,9 +9032,7 @@
       <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="n">
-        <v>0.9728</v>
-      </c>
+      <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="n">
         <v>0.9641</v>
       </c>
@@ -8977,8 +9097,12 @@
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr"/>
       <c r="J39" s="4" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0.9806</v>
+      </c>
       <c r="M39" s="4" t="n">
         <v>0.975</v>
       </c>
@@ -9148,7 +9272,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
@@ -9191,7 +9315,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
@@ -9277,7 +9401,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>QPS2</t>
+          <t>QPS5</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
@@ -9320,7 +9444,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>QPS1</t>
+          <t>QPS4</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
@@ -9363,7 +9487,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>QPS4</t>
+          <t>QPS3</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
@@ -9406,7 +9530,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>QPS3</t>
+          <t>QPS2</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
@@ -9449,7 +9573,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>QPS5</t>
+          <t>QPS1</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
@@ -9562,7 +9686,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr"/>
@@ -9572,10 +9696,18 @@
       <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr"/>
-      <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="n">
+        <v>0.9687</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>1.0079</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>1.0102</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="M54" s="4" t="n">
         <v>0.9968</v>
       </c>
@@ -9583,7 +9715,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr"/>
@@ -9593,12 +9725,8 @@
       <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr"/>
-      <c r="I55" s="4" t="n">
-        <v>0.9687</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>1.0079</v>
-      </c>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="n">
         <v>1.0102</v>
       </c>
@@ -9649,7 +9777,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DRYCGT1</t>
+          <t>DRYCGT3</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
@@ -9692,7 +9820,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>DRYCGT3</t>
+          <t>DRYCGT2</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
@@ -9735,7 +9863,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>DRYCGT2</t>
+          <t>DRYCGT1</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
@@ -9865,7 +9993,9 @@
       <c r="I62" s="4" t="inlineStr"/>
       <c r="J62" s="4" t="inlineStr"/>
       <c r="K62" s="4" t="inlineStr"/>
-      <c r="L62" s="4" t="inlineStr"/>
+      <c r="L62" s="4" t="n">
+        <v>0.9984</v>
+      </c>
       <c r="M62" s="4" t="n">
         <v>0.9994</v>
       </c>
@@ -9885,8 +10015,12 @@
       <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="4" t="inlineStr"/>
       <c r="J63" s="4" t="inlineStr"/>
-      <c r="K63" s="4" t="inlineStr"/>
-      <c r="L63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>0.9993</v>
+      </c>
       <c r="M63" s="4" t="n">
         <v>0.9994</v>
       </c>
@@ -9894,7 +10028,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TORRB4</t>
+          <t>TORRB3</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
@@ -9937,7 +10071,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TORRB3</t>
+          <t>TORRB4</t>
         </is>
       </c>
       <c r="B65" s="4" t="n">
@@ -10175,7 +10309,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>DG_SA1</t>
+          <t>TORNL1</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
@@ -10218,7 +10352,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>TORNL1</t>
+          <t>DG_SA1</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
@@ -10261,7 +10395,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>BOWWPV1</t>
+          <t>BOWWBA1</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr"/>
@@ -10270,15 +10404,9 @@
       <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="inlineStr"/>
-      <c r="H73" s="4" t="n">
-        <v>1.0011</v>
-      </c>
-      <c r="I73" s="4" t="n">
-        <v>1.0002</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>0.9995000000000001</v>
-      </c>
+      <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr"/>
+      <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="n">
         <v>1.0004</v>
       </c>
@@ -10292,27 +10420,15 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>BOLIVAR1</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>1.0054</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="F74" s="4" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>1.0012</v>
-      </c>
+          <t>BOWWDG1</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr"/>
+      <c r="C74" s="4" t="inlineStr"/>
+      <c r="D74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="4" t="n">
         <v>1.0011</v>
       </c>
@@ -10335,15 +10451,27 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>BOWWDG1</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr"/>
-      <c r="C75" s="4" t="inlineStr"/>
-      <c r="D75" s="4" t="inlineStr"/>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
-      <c r="G75" s="4" t="inlineStr"/>
+          <t>BOLIVAR1</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n">
+        <v>1.0045</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>1.0012</v>
+      </c>
       <c r="H75" s="4" t="n">
         <v>1.0011</v>
       </c>
@@ -10366,7 +10494,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>BOWWBA1</t>
+          <t>BOWWPV1</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr"/>
@@ -10375,11 +10503,21 @@
       <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="inlineStr"/>
-      <c r="H76" s="4" t="inlineStr"/>
-      <c r="I76" s="4" t="inlineStr"/>
-      <c r="J76" s="4" t="inlineStr"/>
-      <c r="K76" s="4" t="inlineStr"/>
-      <c r="L76" s="4" t="inlineStr"/>
+      <c r="H76" s="4" t="n">
+        <v>1.0011</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="J76" s="4" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>1.0004</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>0.9999</v>
+      </c>
       <c r="M76" s="4" t="n">
         <v>1.0002</v>
       </c>
@@ -10619,8 +10757,12 @@
       <c r="H83" s="4" t="inlineStr"/>
       <c r="I83" s="4" t="inlineStr"/>
       <c r="J83" s="4" t="inlineStr"/>
-      <c r="K83" s="4" t="inlineStr"/>
-      <c r="L83" s="4" t="inlineStr"/>
+      <c r="K83" s="4" t="n">
+        <v>1.0043</v>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>1.0024</v>
+      </c>
       <c r="M83" s="4" t="n">
         <v>1.0022</v>
       </c>
@@ -10671,20 +10813,42 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>CBWWBA1</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr"/>
-      <c r="C85" s="4" t="inlineStr"/>
-      <c r="D85" s="4" t="inlineStr"/>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr"/>
-      <c r="H85" s="4" t="inlineStr"/>
-      <c r="I85" s="4" t="inlineStr"/>
-      <c r="J85" s="4" t="inlineStr"/>
-      <c r="K85" s="4" t="inlineStr"/>
-      <c r="L85" s="4" t="inlineStr"/>
+          <t>PTSTAN1</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="J85" s="4" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="K85" s="4" t="n">
+        <v>1.0025</v>
+      </c>
+      <c r="L85" s="4" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="M85" s="4" t="n">
         <v>1.0033</v>
       </c>
@@ -10692,20 +10856,42 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ADPBA1</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr"/>
-      <c r="C86" s="4" t="inlineStr"/>
-      <c r="D86" s="4" t="inlineStr"/>
-      <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr"/>
-      <c r="G86" s="4" t="inlineStr"/>
-      <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="4" t="inlineStr"/>
-      <c r="J86" s="4" t="inlineStr"/>
-      <c r="K86" s="4" t="inlineStr"/>
-      <c r="L86" s="4" t="inlineStr"/>
+          <t>STARHLWF</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="K86" s="4" t="n">
+        <v>1.0025</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="M86" s="4" t="n">
         <v>1.0033</v>
       </c>
@@ -10713,16 +10899,30 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>CBWWPV2</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr"/>
-      <c r="C87" s="4" t="inlineStr"/>
-      <c r="D87" s="4" t="inlineStr"/>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr"/>
-      <c r="H87" s="4" t="inlineStr"/>
+          <t>LONSDALE</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I87" s="4" t="n">
         <v>1.0036</v>
       </c>
@@ -10742,7 +10942,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>CBWWPV1</t>
+          <t>CBWWBA1</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr"/>
@@ -10752,12 +10952,8 @@
       <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="inlineStr"/>
       <c r="H88" s="4" t="inlineStr"/>
-      <c r="I88" s="4" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>1.0039</v>
-      </c>
+      <c r="I88" s="4" t="inlineStr"/>
+      <c r="J88" s="4" t="inlineStr"/>
       <c r="K88" s="4" t="n">
         <v>1.0025</v>
       </c>
@@ -10771,30 +10967,16 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>LONSDALE</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F89" s="4" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="G89" s="4" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="H89" s="4" t="n">
-        <v>1.0055</v>
-      </c>
+          <t>CBWWPV1</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr"/>
+      <c r="C89" s="4" t="inlineStr"/>
+      <c r="D89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr"/>
       <c r="I89" s="4" t="n">
         <v>1.0036</v>
       </c>
@@ -10814,7 +10996,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>CBWWBG1</t>
+          <t>CBWWPV2</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr"/>
@@ -10843,30 +11025,16 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C91" s="4" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E91" s="4" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F91" s="4" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="G91" s="4" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="H91" s="4" t="n">
-        <v>1.0055</v>
-      </c>
+          <t>CBWWDG2</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr"/>
+      <c r="C91" s="4" t="inlineStr"/>
+      <c r="D91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="4" t="inlineStr"/>
       <c r="I91" s="4" t="n">
         <v>1.0036</v>
       </c>
@@ -10886,7 +11054,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>CBWWDG2</t>
+          <t>CBWWDG1</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr"/>
@@ -10915,7 +11083,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ADPPV2</t>
+          <t>ADPPV3</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr"/>
@@ -10946,7 +11114,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ADPPV3</t>
+          <t>ADPPV2</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr"/>
@@ -11010,36 +11178,18 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>PTSTAN1</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C96" s="4" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E96" s="4" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F96" s="4" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="I96" s="4" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>1.0039</v>
-      </c>
+          <t>ADPBA1</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr"/>
+      <c r="C96" s="4" t="inlineStr"/>
+      <c r="D96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr"/>
       <c r="K96" s="4" t="n">
         <v>1.0025</v>
       </c>
@@ -11084,7 +11234,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>CBWWDG1</t>
+          <t>CBWWBG1</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr"/>
@@ -11125,8 +11275,12 @@
       <c r="H99" s="4" t="inlineStr"/>
       <c r="I99" s="4" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr"/>
-      <c r="K99" s="4" t="inlineStr"/>
-      <c r="L99" s="4" t="inlineStr"/>
+      <c r="K99" s="4" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="L99" s="4" t="n">
+        <v>1.0072</v>
+      </c>
       <c r="M99" s="4" t="n">
         <v>1.0047</v>
       </c>
@@ -11146,8 +11300,12 @@
       <c r="H100" s="4" t="inlineStr"/>
       <c r="I100" s="4" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr"/>
-      <c r="K100" s="4" t="inlineStr"/>
-      <c r="L100" s="4" t="inlineStr"/>
+      <c r="K100" s="4" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="L100" s="4" t="n">
+        <v>0.9905</v>
+      </c>
       <c r="M100" s="4" t="n">
         <v>1.0056</v>
       </c>
@@ -11210,8 +11368,12 @@
       <c r="H102" s="4" t="inlineStr"/>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr"/>
-      <c r="K102" s="4" t="inlineStr"/>
-      <c r="L102" s="4" t="inlineStr"/>
+      <c r="K102" s="4" t="n">
+        <v>1.0144</v>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>1.0294</v>
+      </c>
       <c r="M102" s="4" t="n">
         <v>1.0083</v>
       </c>
@@ -11262,8 +11424,12 @@
       <c r="H104" s="4" t="inlineStr"/>
       <c r="I104" s="4" t="inlineStr"/>
       <c r="J104" s="4" t="inlineStr"/>
-      <c r="K104" s="4" t="inlineStr"/>
-      <c r="L104" s="4" t="inlineStr"/>
+      <c r="K104" s="4" t="n">
+        <v>0.9964</v>
+      </c>
+      <c r="L104" s="4" t="n">
+        <v>1.0146</v>
+      </c>
       <c r="M104" s="4" t="n">
         <v>1.0112</v>
       </c>
@@ -11346,7 +11512,9 @@
       <c r="I107" s="4" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr"/>
-      <c r="L107" s="4" t="inlineStr"/>
+      <c r="L107" s="4" t="n">
+        <v>0.9992</v>
+      </c>
       <c r="M107" s="4" t="n">
         <v>1.0164</v>
       </c>
@@ -11354,11 +11522,11 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>STANV1</t>
+          <t>HIGHBRY1</t>
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
       <c r="D108" s="4" t="inlineStr"/>
@@ -11396,11 +11564,11 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TEATREE1</t>
+          <t>STANV1</t>
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="C110" s="4" t="inlineStr"/>
       <c r="D110" s="4" t="inlineStr"/>
@@ -11417,11 +11585,11 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>HIGHBRY1</t>
+          <t>ANGAS1</t>
         </is>
       </c>
       <c r="B111" s="4" t="n">
-        <v>1.0042</v>
+        <v>1.0061</v>
       </c>
       <c r="C111" s="4" t="inlineStr"/>
       <c r="D111" s="4" t="inlineStr"/>
@@ -11438,11 +11606,11 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ANGAS2</t>
+          <t>AMCORGR</t>
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1.0061</v>
+        <v>1.0111</v>
       </c>
       <c r="C112" s="4" t="inlineStr"/>
       <c r="D112" s="4" t="inlineStr"/>
@@ -11459,7 +11627,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ANGAS1</t>
+          <t>ANGAS2</t>
         </is>
       </c>
       <c r="B113" s="4" t="n">
@@ -11480,11 +11648,11 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>AMCORGR</t>
+          <t>TEATREE1</t>
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1.0111</v>
+        <v>1.0042</v>
       </c>
       <c r="C114" s="4" t="inlineStr"/>
       <c r="D114" s="4" t="inlineStr"/>
@@ -11524,14 +11692,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>NPS1</t>
+          <t>NPSNL2</t>
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>0.9826</v>
+        <v>1.0482</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>1.0098</v>
+        <v>1.0791</v>
       </c>
       <c r="D116" s="4" t="inlineStr"/>
       <c r="E116" s="4" t="inlineStr"/>
@@ -11547,14 +11715,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>NPS2</t>
+          <t>NPSNL1</t>
         </is>
       </c>
       <c r="B117" s="4" t="n">
-        <v>0.9826</v>
+        <v>0.9929</v>
       </c>
       <c r="C117" s="4" t="n">
-        <v>1.0098</v>
+        <v>1.0132</v>
       </c>
       <c r="D117" s="4" t="inlineStr"/>
       <c r="E117" s="4" t="inlineStr"/>
@@ -11570,14 +11738,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>NPSNL1</t>
+          <t>NPS2</t>
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>0.9929</v>
+        <v>0.9826</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>1.0132</v>
+        <v>1.0098</v>
       </c>
       <c r="D118" s="4" t="inlineStr"/>
       <c r="E118" s="4" t="inlineStr"/>
@@ -11593,14 +11761,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>NPSNL2</t>
+          <t>NPS1</t>
         </is>
       </c>
       <c r="B119" s="4" t="n">
-        <v>1.0482</v>
+        <v>0.9826</v>
       </c>
       <c r="C119" s="4" t="n">
-        <v>1.0791</v>
+        <v>1.0098</v>
       </c>
       <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="4" t="inlineStr"/>
@@ -11616,17 +11784,17 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PEDLER1</t>
+          <t>BLULAKE1</t>
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1.0075</v>
+        <v>1.0062</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>1.0051</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1.0047</v>
+        <v>0.978</v>
       </c>
       <c r="E120" s="4" t="inlineStr"/>
       <c r="F120" s="4" t="inlineStr"/>
@@ -11641,17 +11809,17 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>BLULAKE1</t>
+          <t>PEDLER1</t>
         </is>
       </c>
       <c r="B121" s="4" t="n">
-        <v>1.0062</v>
+        <v>1.0075</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>0.9703000000000001</v>
+        <v>1.0051</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>0.978</v>
+        <v>1.0047</v>
       </c>
       <c r="E121" s="4" t="inlineStr"/>
       <c r="F121" s="4" t="inlineStr"/>
@@ -11691,7 +11859,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>TORRA2</t>
+          <t>TORRA4</t>
         </is>
       </c>
       <c r="B123" s="4" t="n">
@@ -11722,7 +11890,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>TORRA4</t>
+          <t>TORRA2</t>
         </is>
       </c>
       <c r="B124" s="4" t="n">
@@ -11846,30 +12014,24 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>LBBG1</t>
+          <t>TIBG1</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr"/>
       <c r="C128" s="4" t="inlineStr"/>
       <c r="D128" s="4" t="inlineStr"/>
       <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="n">
-        <v>0.9922</v>
-      </c>
-      <c r="G128" s="4" t="n">
-        <v>0.9741</v>
-      </c>
-      <c r="H128" s="4" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="F128" s="4" t="inlineStr"/>
+      <c r="G128" s="4" t="inlineStr"/>
+      <c r="H128" s="4" t="inlineStr"/>
       <c r="I128" s="4" t="n">
-        <v>0.9851</v>
+        <v>1.0001</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>0.979</v>
+        <v>0.9996</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0.9841</v>
+        <v>0.9998</v>
       </c>
       <c r="L128" s="4" t="inlineStr"/>
       <c r="M128" s="4" t="inlineStr"/>
@@ -11877,7 +12039,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>HVWWBA1G</t>
+          <t>BOWWBA1G</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr"/>
@@ -11887,16 +12049,16 @@
       <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="inlineStr"/>
       <c r="H129" s="4" t="n">
-        <v>1.0052</v>
+        <v>1.0011</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>1.003</v>
+        <v>1.0002</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>1.0041</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1.0043</v>
+        <v>1.0004</v>
       </c>
       <c r="L129" s="4" t="inlineStr"/>
       <c r="M129" s="4" t="inlineStr"/>
@@ -11904,34 +12066,30 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>HPRG1</t>
+          <t>LBBG1</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr"/>
       <c r="C130" s="4" t="inlineStr"/>
-      <c r="D130" s="4" t="n">
-        <v>0.9848</v>
-      </c>
-      <c r="E130" s="4" t="n">
-        <v>0.9771</v>
-      </c>
+      <c r="D130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr"/>
       <c r="F130" s="4" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>0.9741</v>
+      </c>
+      <c r="H130" s="4" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="I130" s="4" t="n">
         <v>0.9851</v>
       </c>
-      <c r="G130" s="4" t="n">
-        <v>0.9838</v>
-      </c>
-      <c r="H130" s="4" t="n">
-        <v>0.9772</v>
-      </c>
-      <c r="I130" s="4" t="n">
-        <v>0.9651999999999999</v>
-      </c>
       <c r="J130" s="4" t="n">
-        <v>0.9653</v>
+        <v>0.979</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0.9657</v>
+        <v>0.9841</v>
       </c>
       <c r="L130" s="4" t="inlineStr"/>
       <c r="M130" s="4" t="inlineStr"/>
@@ -11939,7 +12097,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TIBG1</t>
+          <t>HVWWBA1G</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr"/>
@@ -11948,15 +12106,17 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="inlineStr"/>
-      <c r="H131" s="4" t="inlineStr"/>
+      <c r="H131" s="4" t="n">
+        <v>1.0052</v>
+      </c>
       <c r="I131" s="4" t="n">
-        <v>1.0001</v>
+        <v>1.003</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>0.9996</v>
+        <v>1.0041</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0.9998</v>
+        <v>1.0043</v>
       </c>
       <c r="L131" s="4" t="inlineStr"/>
       <c r="M131" s="4" t="inlineStr"/>
@@ -11964,34 +12124,24 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>DALNTH01</t>
+          <t>CBWWBA1G</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr"/>
       <c r="C132" s="4" t="inlineStr"/>
-      <c r="D132" s="4" t="n">
-        <v>0.8848</v>
-      </c>
-      <c r="E132" s="4" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="F132" s="4" t="n">
-        <v>0.9045</v>
-      </c>
-      <c r="G132" s="4" t="n">
-        <v>0.9193</v>
-      </c>
-      <c r="H132" s="4" t="n">
-        <v>0.9212</v>
-      </c>
+      <c r="D132" s="4" t="inlineStr"/>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
+      <c r="G132" s="4" t="inlineStr"/>
+      <c r="H132" s="4" t="inlineStr"/>
       <c r="I132" s="4" t="n">
-        <v>0.9432</v>
+        <v>1.0036</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>0.8954</v>
+        <v>1.0039</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0.9092</v>
+        <v>1.0025</v>
       </c>
       <c r="L132" s="4" t="inlineStr"/>
       <c r="M132" s="4" t="inlineStr"/>
@@ -11999,26 +12149,34 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>BOWWBA1G</t>
+          <t>HPRG1</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr"/>
       <c r="C133" s="4" t="inlineStr"/>
-      <c r="D133" s="4" t="inlineStr"/>
-      <c r="E133" s="4" t="inlineStr"/>
-      <c r="F133" s="4" t="inlineStr"/>
-      <c r="G133" s="4" t="inlineStr"/>
+      <c r="D133" s="4" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>0.9838</v>
+      </c>
       <c r="H133" s="4" t="n">
-        <v>1.0011</v>
+        <v>0.9772</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>1.0002</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9653</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1.0004</v>
+        <v>0.9657</v>
       </c>
       <c r="L133" s="4" t="inlineStr"/>
       <c r="M133" s="4" t="inlineStr"/>
@@ -12026,28 +12184,34 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>ADPBA1G</t>
+          <t>DALNTH01</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr"/>
       <c r="C134" s="4" t="inlineStr"/>
-      <c r="D134" s="4" t="inlineStr"/>
-      <c r="E134" s="4" t="inlineStr"/>
-      <c r="F134" s="4" t="inlineStr"/>
+      <c r="D134" s="4" t="n">
+        <v>0.8848</v>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>0.9045</v>
+      </c>
       <c r="G134" s="4" t="n">
-        <v>1.0038</v>
+        <v>0.9193</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>1.0055</v>
+        <v>0.9212</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>1.0036</v>
+        <v>0.9432</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>1.0039</v>
+        <v>0.8954</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1.0025</v>
+        <v>0.9092</v>
       </c>
       <c r="L134" s="4" t="inlineStr"/>
       <c r="M134" s="4" t="inlineStr"/>
@@ -12055,7 +12219,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>CBWWBA1G</t>
+          <t>ADPBA1G</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr"/>
@@ -12063,8 +12227,12 @@
       <c r="D135" s="4" t="inlineStr"/>
       <c r="E135" s="4" t="inlineStr"/>
       <c r="F135" s="4" t="inlineStr"/>
-      <c r="G135" s="4" t="inlineStr"/>
-      <c r="H135" s="4" t="inlineStr"/>
+      <c r="G135" s="4" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="H135" s="4" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I135" s="4" t="n">
         <v>1.0036</v>
       </c>
@@ -12349,41 +12517,41 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MWPS3PV1</t>
+          <t>MANNUMB1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Morgan-Whyalla Pipeline Pumping Station No 3</t>
+          <t>Mannum Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.9741</v>
+        <v>1.0083</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.9897</v>
+        <v>1.0294</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-0.0156</v>
+        <v>-0.0211</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-1.58</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MAPS2PV1</t>
+          <t>MWPS3PV1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Mannum - Adelaide Pipeline Pumping Station No 2, PV Units 1-6</t>
+          <t>Morgan-Whyalla Pipeline Pumping Station No 3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -12392,27 +12560,27 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.0134</v>
+        <v>0.9741</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.0257</v>
+        <v>0.9897</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.0123</v>
+        <v>-0.0156</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-1.2</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MAPS3PV1</t>
+          <t>MAPS2PV1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Mannum - Adelaide Pipeline Pumping Station No 3, PV Units 1-6</t>
+          <t>Mannum - Adelaide Pipeline Pumping Station No 2, PV Units 1-6</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -12421,27 +12589,27 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.0137</v>
+        <v>1.0134</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.0252</v>
+        <v>1.0257</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.0115</v>
+        <v>-0.0123</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-1.12</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MWPS4PV1</t>
+          <t>MAPS3PV1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Morgan-Whyalla Pipeline Pumping Station No 4</t>
+          <t>Mannum - Adelaide Pipeline Pumping Station No 3, PV Units 1-6</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -12450,80 +12618,80 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.9772999999999999</v>
+        <v>1.0137</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.9837</v>
+        <v>1.0252</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.0064</v>
+        <v>-0.0115</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.65</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>POR03</t>
+          <t>MWPS4PV1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Port Lincoln Gas Turbine</t>
+          <t>Morgan-Whyalla Pipeline Pumping Station No 4</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.9865</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.9916</v>
+        <v>0.9837</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.0051</v>
+        <v>-0.0064</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.51</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CATHROCK</t>
+          <t>HPR1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Cathedral Rocks</t>
+          <t>Hornsdale Power Reserve</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.9417</v>
+        <v>0.975</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.9467</v>
+        <v>0.9806</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.005</v>
+        <v>-0.0056</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.53</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>POR01</t>
+          <t>POR03</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -12537,85 +12705,85 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.9846</v>
+        <v>0.9865</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.9895</v>
+        <v>0.9916</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.0049</v>
+        <v>-0.0051</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AGLHAL</t>
+          <t>CATHROCK</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Hallett Power Station</t>
+          <t>Cathedral Rocks</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.9628</v>
+        <v>0.9417</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.9663</v>
+        <v>0.9467</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.0035</v>
+        <v>-0.005</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.36</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>POR01</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Hallett 1 Wind Farm</t>
+          <t>Port Lincoln Gas Turbine</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.9628</v>
+        <v>0.9846</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9663</v>
+        <v>0.9895</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.0035</v>
+        <v>-0.0049</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.36</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MINTARO</t>
+          <t>AGLHAL</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Mintaro Gas Turbine Station</t>
+          <t>Hallett Power Station</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -12624,27 +12792,27 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9621</v>
+        <v>0.9628</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.9651</v>
+        <v>0.9663</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.003</v>
+        <v>-0.0035</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.31</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LGAPWF2</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Lincoln Gap Wind Farm</t>
+          <t>Hallett 1 Wind Farm</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -12653,85 +12821,85 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9661</v>
+        <v>0.9628</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9689</v>
+        <v>0.9663</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.0028</v>
+        <v>-0.0035</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.29</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LGAPWF1</t>
+          <t>TEMPB1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Lincoln Gap Wind Farm</t>
+          <t>Templers Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.9661</v>
+        <v>1.0112</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9689</v>
+        <v>1.0146</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.0028</v>
+        <v>-0.0034</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.29</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HDWF1</t>
+          <t>MINTARO</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm</t>
+          <t>Mintaro Gas Turbine Station</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.9533</v>
+        <v>0.9621</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.956</v>
+        <v>0.9651</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.0027</v>
+        <v>-0.003</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.28</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HDWF2</t>
+          <t>LGAPWF2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 2</t>
+          <t>Lincoln Gap Wind Farm</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -12740,27 +12908,27 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.9533</v>
+        <v>0.9661</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.956</v>
+        <v>0.9689</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.0027</v>
+        <v>-0.0028</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HDWF3</t>
+          <t>LGAPWF1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 3</t>
+          <t>Lincoln Gap Wind Farm</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -12769,56 +12937,56 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.9533</v>
+        <v>0.9661</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.956</v>
+        <v>0.9689</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.0027</v>
+        <v>-0.0028</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PAREPS1</t>
+          <t>LGAPBS1</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Port Augusta Renewable Energy Park</t>
+          <t xml:space="preserve">Lincoln Gap Wind Farm Battery </t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9709</v>
+        <v>0.9661</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9735</v>
+        <v>0.9689</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.0026</v>
+        <v>-0.0028</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.27</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>PAREPW1</t>
+          <t>HDWF3</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Port Augusta Renewable Energy Park</t>
+          <t>Hornsdale Wind Farm 3</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -12827,27 +12995,27 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.9709</v>
+        <v>0.9533</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.9735</v>
+        <v>0.956</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.0026</v>
+        <v>-0.0027</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SNOWTWN1</t>
+          <t>HDWF2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Snowtown Wind Farm Units 1 And 47</t>
+          <t>Hornsdale Wind Farm 2</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -12856,16 +13024,16 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.9132</v>
+        <v>0.9533</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.9157</v>
+        <v>0.956</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.0025</v>
+        <v>-0.0027</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="25">
@@ -12915,7 +13083,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -12944,7 +13112,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -13031,41 +13199,41 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>CGBESS01</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 3 Wind Farm</t>
+          <t>Clements Gap BESS</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.9468</v>
+        <v>1.0164</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.9297</v>
+        <v>0.9992</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.0171</v>
+        <v>0.0172</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Lake Bonney Wind Farm Stage 1</t>
+          <t>Lake Bonney Stage 3 Wind Farm</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -13118,99 +13286,99 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TATIARA1</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Tataria Bordertown Plant</t>
+          <t>Lake Bonney Wind Farm Stage 1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.0032</v>
+        <v>0.9468</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.9925</v>
+        <v>0.9297</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.0107</v>
+        <v>0.0171</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1.08</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MANNSF2</t>
+          <t>LBB1</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Mannum 2 Solar Farm</t>
+          <t>Lake Bonney BESS1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.9959</v>
+        <v>1.0056</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.9932</v>
+        <v>0.9905</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.0027</v>
+        <v>0.0151</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.27</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TBSF1</t>
+          <t>TATIARA1</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Tailem Bend Solar Project 1</t>
+          <t>Tataria Bordertown Plant</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.9978</v>
+        <v>1.0032</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.9952</v>
+        <v>0.9925</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.0026</v>
+        <v>0.0107</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.26</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>MANNSF2</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Tailem Bend 2 Hybrid Renewable Power Station</t>
+          <t>Mannum 2 Solar Farm</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -13219,277 +13387,277 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>0.9968</v>
+        <v>0.9959</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9932</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.0023</v>
+        <v>0.0027</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>WPWF</t>
+          <t>TBSF1</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Wattle Point Wind Farm</t>
+          <t>Tailem Bend Solar Project 1</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0.8476</v>
+        <v>0.9978</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.8456</v>
+        <v>0.9952</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.002</v>
+        <v>0.0026</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>BOLIVPS1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Bolivar Power Station</t>
+          <t>Tailem Bend 2 Hybrid Renewable Power Station</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>1.0019</v>
+        <v>0.9968</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.0019</v>
+        <v>0.0023</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SNAPPER1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Snapper Point Power Station</t>
+          <t>Tailem Bend 2 Hybrid Renewable Power Station</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.9999</v>
+        <v>0.9968</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.9987</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0023</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>CLEMGPWF</t>
+          <t>DALNTH1</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Clements Gap Wind Farm</t>
+          <t>Dalrymple North BESS</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>0.9614</v>
+        <v>0.9358</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.9604</v>
+        <v>0.9337</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.001</v>
+        <v>0.0021</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>PPCCGT</t>
+          <t>WPWF</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Pelican Point Power Station</t>
+          <t>Wattle Point Wind Farm</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0.9992</v>
+        <v>0.8476</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.9983</v>
+        <v>0.8456</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.0009</v>
+        <v>0.002</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>BOLIVPS1</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Snowtown Wind Farm Stage 2 North</t>
+          <t>Bolivar Power Station</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.9699</v>
+        <v>1.0019</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.9695</v>
+        <v>1</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0019</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNAPPER1</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Snowtown South Wind Farm</t>
+          <t>Snapper Point Power Station</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>0.9699</v>
+        <v>0.9999</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.9695</v>
+        <v>0.9987</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0012</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TORRB4</t>
+          <t>CLEMGPWF</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Torrens Island Power Station</t>
+          <t>Clements Gap Wind Farm</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.9996</v>
+        <v>0.9614</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.9992</v>
+        <v>0.9604</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.001</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TORRB3</t>
+          <t>BUNGAMB1</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Torrens Island Power Station</t>
+          <t>Bungama Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0.9996</v>
+        <v>0.9994</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.9992</v>
+        <v>0.9984</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/SA_mlf.xlsx
+++ b/outputs/SA_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -991,12 +991,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 3 Wind Farm</t>
+          <t>Lake Bonney Wind Farm Stage 1</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>39</v>
+        <v>80.5</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>0.9352</v>
@@ -1125,12 +1125,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Wind Farm Stage 1</t>
+          <t>Lake Bonney Stage 3 Wind Farm</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>80.5</v>
+        <v>39</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>0.9352</v>
@@ -1259,12 +1259,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>HDWF2</t>
+          <t>HDWF1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 2</t>
+          <t>Hornsdale Wind Farm</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1275,9 +1275,11 @@
       <c r="D12" s="4" t="n">
         <v>102.4</v>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0.9792999999999999</v>
+      </c>
       <c r="F12" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0.9841</v>
@@ -1324,12 +1326,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HDWF1</t>
+          <t>HDWF2</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm</t>
+          <t>Hornsdale Wind Farm 2</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1340,11 +1342,9 @@
       <c r="D13" s="4" t="n">
         <v>102.4</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>0.9792999999999999</v>
-      </c>
+      <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9918</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.9841</v>
@@ -1511,12 +1511,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>BLUFF1</t>
+          <t>NBHWF1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>The Bluff Wind Farm</t>
+          <t>North Brown Hill Wind Farm</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>52.5</v>
+        <v>132.3</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>0.9767</v>
@@ -1578,12 +1578,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>NBHWF1</t>
+          <t>BLUFF1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>North Brown Hill Wind Farm</t>
+          <t>The Bluff Wind Farm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>132.3</v>
+        <v>52.5</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0.9767</v>
@@ -1645,7 +1645,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>SNUG2</t>
+          <t>SNUG3</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1712,7 +1712,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>SNUG3</t>
+          <t>SNUG2</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2108,21 +2108,21 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>AGLHAL</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Hallett Power Station</t>
+          <t>Hallett 1 Wind Farm</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>217</v>
+        <v>94.5</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>0.9835</v>
@@ -2175,21 +2175,21 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>AGLHAL</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Hallett 1 Wind Farm</t>
+          <t>Hallett Power Station</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>94.5</v>
+        <v>217</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0.9835</v>
@@ -2411,118 +2411,118 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>LGAPWF1</t>
+          <t>LGAPBS1</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Lincoln Gap Wind Farm</t>
+          <t xml:space="preserve">Lincoln Gap Wind Farm Battery </t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>126</v>
+        <v>10.8</v>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="n">
-        <v>0.9947</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>0.9821</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0.9779</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0.9628</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>0.9601</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0.9576</v>
-      </c>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
       <c r="O30" s="5" t="inlineStr"/>
       <c r="P30" s="5" t="n">
         <v>0.9689</v>
       </c>
-      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="n">
+        <v>0.9689</v>
+      </c>
       <c r="R30" s="5" t="n">
         <v>0.9661</v>
       </c>
-      <c r="S30" s="5" t="inlineStr"/>
+      <c r="S30" s="5" t="n">
+        <v>0.9661</v>
+      </c>
       <c r="T30" s="5" t="n">
         <v>-0.0028</v>
       </c>
       <c r="U30" s="6" t="n">
         <v>-0.29</v>
       </c>
-      <c r="V30" s="5" t="inlineStr"/>
-      <c r="W30" s="6" t="inlineStr"/>
+      <c r="V30" s="5" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="W30" s="6" t="n">
+        <v>-0.29</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>LGAPBS1</t>
+          <t>LGAPWF1</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lincoln Gap Wind Farm Battery </t>
+          <t>Lincoln Gap Wind Farm</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.8</v>
+        <v>126</v>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="n">
+        <v>0.9947</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.9821</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0.9628</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>0.9601</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0.9576</v>
+      </c>
       <c r="O31" s="5" t="inlineStr"/>
       <c r="P31" s="5" t="n">
         <v>0.9689</v>
       </c>
-      <c r="Q31" s="5" t="n">
-        <v>0.9689</v>
-      </c>
+      <c r="Q31" s="5" t="inlineStr"/>
       <c r="R31" s="5" t="n">
         <v>0.9661</v>
       </c>
-      <c r="S31" s="5" t="n">
-        <v>0.9661</v>
-      </c>
+      <c r="S31" s="5" t="inlineStr"/>
       <c r="T31" s="5" t="n">
         <v>-0.0028</v>
       </c>
       <c r="U31" s="6" t="n">
         <v>-0.29</v>
       </c>
-      <c r="V31" s="5" t="n">
-        <v>-0.0028</v>
-      </c>
-      <c r="W31" s="6" t="n">
-        <v>-0.29</v>
-      </c>
+      <c r="V31" s="5" t="inlineStr"/>
+      <c r="W31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -2745,12 +2745,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Snowtown South Wind Farm</t>
+          <t>Snowtown Wind Farm Stage 2 North</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>0.9782</v>
@@ -2812,12 +2812,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Snowtown Wind Farm Stage 2 North</t>
+          <t>Snowtown South Wind Farm</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>0.9782</v>
@@ -2879,12 +2879,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>BNGSF1</t>
+          <t>BNGSF2</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Bungala One Solar Farm</t>
+          <t>Bungala Two Solar Farm</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2897,9 +2897,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="n">
-        <v>0.9946</v>
-      </c>
+      <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="n">
         <v>0.97</v>
       </c>
@@ -2942,12 +2940,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>BNGSF2</t>
+          <t>BNGSF1</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Bungala Two Solar Farm</t>
+          <t>Bungala One Solar Farm</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2960,7 +2958,9 @@
       </c>
       <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="n">
+        <v>0.9946</v>
+      </c>
       <c r="H39" s="5" t="n">
         <v>0.97</v>
       </c>
@@ -3485,7 +3485,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3552,7 +3552,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3745,7 +3745,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>QPS1</t>
+          <t>QPS5</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>0.9932</v>
@@ -3812,7 +3812,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>QPS2</t>
+          <t>QPS3</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3879,7 +3879,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>QPS3</t>
+          <t>QPS4</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3946,7 +3946,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>QPS4</t>
+          <t>QPS2</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4013,7 +4013,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>QPS5</t>
+          <t>QPS1</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>0.9932</v>
@@ -4198,7 +4198,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4208,11 +4208,11 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="E59" s="5" t="inlineStr"/>
       <c r="F59" s="5" t="inlineStr"/>
@@ -4221,43 +4221,37 @@
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
       <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="inlineStr"/>
-      <c r="M59" s="5" t="inlineStr"/>
+      <c r="L59" s="5" t="n">
+        <v>0.9687</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>1.0079</v>
+      </c>
       <c r="N59" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="O59" s="5" t="n">
-        <v>1.0102</v>
-      </c>
+      <c r="O59" s="5" t="inlineStr"/>
       <c r="P59" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="Q59" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+      <c r="Q59" s="5" t="inlineStr"/>
       <c r="R59" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="S59" s="5" t="n">
-        <v>0.9968</v>
-      </c>
+      <c r="S59" s="5" t="inlineStr"/>
       <c r="T59" s="5" t="n">
         <v>0.0023</v>
       </c>
       <c r="U59" s="6" t="n">
         <v>0.23</v>
       </c>
-      <c r="V59" s="5" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="W59" s="6" t="n">
-        <v>0.23</v>
-      </c>
+      <c r="V59" s="5" t="inlineStr"/>
+      <c r="W59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -4267,11 +4261,11 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="5" t="inlineStr"/>
@@ -4280,32 +4274,38 @@
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="5" t="inlineStr"/>
-      <c r="L60" s="5" t="n">
-        <v>0.9687</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>1.0079</v>
-      </c>
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr"/>
       <c r="N60" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="O60" s="5" t="inlineStr"/>
+      <c r="O60" s="5" t="n">
+        <v>1.0102</v>
+      </c>
       <c r="P60" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="Q60" s="5" t="inlineStr"/>
+      <c r="Q60" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="R60" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="S60" s="5" t="inlineStr"/>
+      <c r="S60" s="5" t="n">
+        <v>0.9968</v>
+      </c>
       <c r="T60" s="5" t="n">
         <v>0.0023</v>
       </c>
       <c r="U60" s="6" t="n">
         <v>0.23</v>
       </c>
-      <c r="V60" s="5" t="inlineStr"/>
-      <c r="W60" s="6" t="inlineStr"/>
+      <c r="V60" s="5" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="W60" s="6" t="n">
+        <v>0.23</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -4371,7 +4371,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT3</t>
+          <t>DRYCGT2</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4438,7 +4438,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT2</t>
+          <t>DRYCGT3</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4690,7 +4690,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>TORRB1</t>
+          <t>TORRB4</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4757,7 +4757,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>TORRB2</t>
+          <t>TORRB1</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -4891,7 +4891,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>TORRB4</t>
+          <t>TORRB2</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4958,128 +4958,128 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>TIB1</t>
+          <t>OSB-AG</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Torrens Island BESS</t>
+          <t>Osborne Power Station</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="E71" s="5" t="inlineStr"/>
-      <c r="F71" s="5" t="inlineStr"/>
-      <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="5" t="inlineStr"/>
-      <c r="K71" s="5" t="inlineStr"/>
-      <c r="L71" s="5" t="inlineStr"/>
-      <c r="M71" s="5" t="inlineStr"/>
+        <v>180</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>0.9992</v>
+      </c>
       <c r="N71" s="5" t="n">
-        <v>0.9996</v>
-      </c>
-      <c r="O71" s="5" t="n">
-        <v>0.9998</v>
-      </c>
+        <v>0.9994</v>
+      </c>
+      <c r="O71" s="5" t="inlineStr"/>
       <c r="P71" s="5" t="n">
-        <v>0.9993</v>
-      </c>
-      <c r="Q71" s="5" t="n">
-        <v>0.9992</v>
-      </c>
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="Q71" s="5" t="inlineStr"/>
       <c r="R71" s="5" t="n">
         <v>0.9997</v>
       </c>
-      <c r="S71" s="5" t="n">
-        <v>0.9994</v>
-      </c>
+      <c r="S71" s="5" t="inlineStr"/>
       <c r="T71" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0002</v>
       </c>
       <c r="U71" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V71" s="5" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="W71" s="6" t="n">
         <v>0.02</v>
       </c>
+      <c r="V71" s="5" t="inlineStr"/>
+      <c r="W71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>OSB-AG</t>
+          <t>TIB1</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Osborne Power Station</t>
+          <t>Torrens Island BESS</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>0.9994</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>0.9988</v>
-      </c>
-      <c r="H72" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="inlineStr"/>
+      <c r="L72" s="5" t="inlineStr"/>
+      <c r="M72" s="5" t="inlineStr"/>
+      <c r="N72" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="O72" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="P72" s="5" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="Q72" s="5" t="n">
         <v>0.9992</v>
       </c>
-      <c r="I72" s="5" t="n">
-        <v>0.9997</v>
-      </c>
-      <c r="J72" s="5" t="n">
-        <v>0.9998</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>0.9999</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>0.9999</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>0.9992</v>
-      </c>
-      <c r="N72" s="5" t="n">
-        <v>0.9994</v>
-      </c>
-      <c r="O72" s="5" t="inlineStr"/>
-      <c r="P72" s="5" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="Q72" s="5" t="inlineStr"/>
       <c r="R72" s="5" t="n">
         <v>0.9997</v>
       </c>
-      <c r="S72" s="5" t="inlineStr"/>
+      <c r="S72" s="5" t="n">
+        <v>0.9994</v>
+      </c>
       <c r="T72" s="5" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="U72" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V72" s="5" t="n">
         <v>0.0002</v>
       </c>
-      <c r="U72" s="6" t="n">
+      <c r="W72" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V72" s="5" t="inlineStr"/>
-      <c r="W72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -5139,47 +5139,51 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>BARKIPS1</t>
+          <t>DG_SA1</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Barker Inlet Power Station</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+          <t>SA1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr"/>
       <c r="D74" s="4" t="n">
-        <v>211</v>
-      </c>
-      <c r="E74" s="5" t="inlineStr"/>
-      <c r="F74" s="5" t="inlineStr"/>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="5" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I74" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="M74" s="5" t="n">
         <v>1</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="O74" s="5" t="inlineStr"/>
       <c r="P74" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="Q74" s="5" t="inlineStr"/>
       <c r="R74" s="5" t="n">
@@ -5187,10 +5191,10 @@
       </c>
       <c r="S74" s="5" t="inlineStr"/>
       <c r="T74" s="5" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="U74" s="6" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="V74" s="5" t="inlineStr"/>
       <c r="W74" s="6" t="inlineStr"/>
@@ -5198,12 +5202,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>TORNL1</t>
+          <t>BARKIPS1</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>TORRENS ISLAND POWER STATION</t>
+          <t>Barker Inlet Power Station</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -5212,41 +5216,33 @@
         </is>
       </c>
       <c r="D75" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="E75" s="5" t="inlineStr"/>
+      <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr"/>
       <c r="I75" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="M75" s="5" t="n">
         <v>1</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="O75" s="5" t="inlineStr"/>
       <c r="P75" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="Q75" s="5" t="inlineStr"/>
       <c r="R75" s="5" t="n">
@@ -5254,10 +5250,10 @@
       </c>
       <c r="S75" s="5" t="inlineStr"/>
       <c r="T75" s="5" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="U75" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="V75" s="5" t="inlineStr"/>
       <c r="W75" s="6" t="inlineStr"/>
@@ -5265,17 +5261,21 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>DG_SA1</t>
+          <t>TORNL1</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>SA1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr"/>
+          <t>TORRENS ISLAND POWER STATION</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D76" s="4" t="n">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="E76" s="5" t="n">
         <v>1</v>
@@ -5328,7 +5328,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>BOLIVAR1</t>
+          <t>BOWWDG1</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5338,30 +5338,18 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>1.0054</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="J77" s="5" t="n">
-        <v>1.0012</v>
-      </c>
+        <v>0.66</v>
+      </c>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr"/>
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr"/>
       <c r="K77" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -5454,7 +5442,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>BOWWDG1</t>
+          <t>BOLIVAR1</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5464,18 +5452,30 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D79" s="4" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E79" s="5" t="inlineStr"/>
-      <c r="F79" s="5" t="inlineStr"/>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr"/>
-      <c r="I79" s="5" t="inlineStr"/>
-      <c r="J79" s="5" t="inlineStr"/>
+        <v>9.9</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>1.0045</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>1.0012</v>
+      </c>
       <c r="K79" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -5924,7 +5924,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>HVWWPV1</t>
+          <t>HVWWBA1</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -5934,11 +5934,11 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E87" s="5" t="inlineStr"/>
       <c r="F87" s="5" t="inlineStr"/>
@@ -5946,40 +5946,44 @@
       <c r="H87" s="5" t="inlineStr"/>
       <c r="I87" s="5" t="inlineStr"/>
       <c r="J87" s="5" t="inlineStr"/>
-      <c r="K87" s="5" t="n">
-        <v>1.0052</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="M87" s="5" t="n">
-        <v>1.0041</v>
-      </c>
+      <c r="K87" s="5" t="inlineStr"/>
+      <c r="L87" s="5" t="inlineStr"/>
+      <c r="M87" s="5" t="inlineStr"/>
       <c r="N87" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="O87" s="5" t="inlineStr"/>
+      <c r="O87" s="5" t="n">
+        <v>1.0043</v>
+      </c>
       <c r="P87" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="Q87" s="5" t="inlineStr"/>
+      <c r="Q87" s="5" t="n">
+        <v>1.0024</v>
+      </c>
       <c r="R87" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="S87" s="5" t="inlineStr"/>
+      <c r="S87" s="5" t="n">
+        <v>1.0022</v>
+      </c>
       <c r="T87" s="5" t="n">
         <v>-0.0002</v>
       </c>
       <c r="U87" s="6" t="n">
         <v>-0.02</v>
       </c>
-      <c r="V87" s="5" t="inlineStr"/>
-      <c r="W87" s="6" t="inlineStr"/>
+      <c r="V87" s="5" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="W87" s="6" t="n">
+        <v>-0.02</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>HVWWBA1</t>
+          <t>HVWWPV1</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -5989,11 +5993,11 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E88" s="5" t="inlineStr"/>
       <c r="F88" s="5" t="inlineStr"/>
@@ -6001,39 +6005,35 @@
       <c r="H88" s="5" t="inlineStr"/>
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="5" t="inlineStr"/>
-      <c r="K88" s="5" t="inlineStr"/>
-      <c r="L88" s="5" t="inlineStr"/>
-      <c r="M88" s="5" t="inlineStr"/>
+      <c r="K88" s="5" t="n">
+        <v>1.0052</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>1.0041</v>
+      </c>
       <c r="N88" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="O88" s="5" t="n">
-        <v>1.0043</v>
-      </c>
+      <c r="O88" s="5" t="inlineStr"/>
       <c r="P88" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="Q88" s="5" t="n">
-        <v>1.0024</v>
-      </c>
+      <c r="Q88" s="5" t="inlineStr"/>
       <c r="R88" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="S88" s="5" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="S88" s="5" t="inlineStr"/>
       <c r="T88" s="5" t="n">
         <v>-0.0002</v>
       </c>
       <c r="U88" s="6" t="n">
         <v>-0.02</v>
       </c>
-      <c r="V88" s="5" t="n">
-        <v>-0.0002</v>
-      </c>
-      <c r="W88" s="6" t="n">
-        <v>-0.02</v>
-      </c>
+      <c r="V88" s="5" t="inlineStr"/>
+      <c r="W88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -6105,40 +6105,28 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>PTSTAN1</t>
+          <t>ADPPV2</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Pt Stanvac Power Station</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I90" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>1.005</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="E90" s="5" t="inlineStr"/>
+      <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr"/>
+      <c r="H90" s="5" t="inlineStr"/>
+      <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="5" t="inlineStr"/>
       <c r="K90" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -6172,40 +6160,28 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
+          <t>ADPPV3</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Starfish Hill Wind Farm</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>1.005</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="E91" s="5" t="inlineStr"/>
+      <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr"/>
+      <c r="H91" s="5" t="inlineStr"/>
+      <c r="I91" s="5" t="inlineStr"/>
+      <c r="J91" s="5" t="inlineStr"/>
       <c r="K91" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -6239,39 +6215,29 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>LONSDALE</t>
+          <t>ADPPV1</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Lonsdale Power Station</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>1.0053</v>
-      </c>
+        <v>24.75</v>
+      </c>
+      <c r="E92" s="5" t="inlineStr"/>
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr"/>
+      <c r="H92" s="5" t="inlineStr"/>
+      <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="5" t="n">
-        <v>1.005</v>
+        <v>1.0038</v>
       </c>
       <c r="K92" s="5" t="n">
         <v>1.0055</v>
@@ -6306,21 +6272,21 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1</t>
+          <t>ADPMH1</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="E93" s="5" t="inlineStr"/>
       <c r="F93" s="5" t="inlineStr"/>
@@ -6328,49 +6294,45 @@
       <c r="H93" s="5" t="inlineStr"/>
       <c r="I93" s="5" t="inlineStr"/>
       <c r="J93" s="5" t="inlineStr"/>
-      <c r="K93" s="5" t="inlineStr"/>
-      <c r="L93" s="5" t="inlineStr"/>
-      <c r="M93" s="5" t="inlineStr"/>
+      <c r="K93" s="5" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="N93" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O93" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="O93" s="5" t="inlineStr"/>
       <c r="P93" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q93" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="Q93" s="5" t="inlineStr"/>
       <c r="R93" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S93" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="S93" s="5" t="inlineStr"/>
       <c r="T93" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U93" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V93" s="5" t="n">
-        <v>-0.0004</v>
-      </c>
-      <c r="W93" s="6" t="n">
-        <v>-0.04</v>
-      </c>
+      <c r="V93" s="5" t="inlineStr"/>
+      <c r="W93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG2</t>
+          <t>LONSDALE</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Lonsdale Power Station</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -6379,15 +6341,29 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E94" s="5" t="inlineStr"/>
-      <c r="F94" s="5" t="inlineStr"/>
-      <c r="G94" s="5" t="inlineStr"/>
-      <c r="H94" s="5" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr"/>
-      <c r="J94" s="5" t="inlineStr"/>
-      <c r="K94" s="5" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L94" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6418,29 +6394,43 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV1</t>
+          <t>PTSTAN1</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Pt Stanvac Power Station</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E95" s="5" t="inlineStr"/>
-      <c r="F95" s="5" t="inlineStr"/>
-      <c r="G95" s="5" t="inlineStr"/>
-      <c r="H95" s="5" t="inlineStr"/>
-      <c r="I95" s="5" t="inlineStr"/>
-      <c r="J95" s="5" t="inlineStr"/>
-      <c r="K95" s="5" t="inlineStr"/>
+        <v>57.6</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L95" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6471,29 +6461,43 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV2</t>
+          <t>STARHLWF</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Starfish Hill Wind Farm</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="5" t="inlineStr"/>
-      <c r="G96" s="5" t="inlineStr"/>
-      <c r="H96" s="5" t="inlineStr"/>
-      <c r="I96" s="5" t="inlineStr"/>
-      <c r="J96" s="5" t="inlineStr"/>
-      <c r="K96" s="5" t="inlineStr"/>
+        <v>34.5</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L96" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6524,21 +6528,21 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>ADPPV3</t>
+          <t>CBWWBA1</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>0.02</v>
+        <v>2.16</v>
       </c>
       <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="5" t="inlineStr"/>
@@ -6546,35 +6550,39 @@
       <c r="H97" s="5" t="inlineStr"/>
       <c r="I97" s="5" t="inlineStr"/>
       <c r="J97" s="5" t="inlineStr"/>
-      <c r="K97" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="M97" s="5" t="n">
-        <v>1.0039</v>
-      </c>
+      <c r="K97" s="5" t="inlineStr"/>
+      <c r="L97" s="5" t="inlineStr"/>
+      <c r="M97" s="5" t="inlineStr"/>
       <c r="N97" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O97" s="5" t="inlineStr"/>
+      <c r="O97" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="P97" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q97" s="5" t="inlineStr"/>
+      <c r="Q97" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="R97" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S97" s="5" t="inlineStr"/>
+      <c r="S97" s="5" t="n">
+        <v>1.0033</v>
+      </c>
       <c r="T97" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U97" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V97" s="5" t="inlineStr"/>
-      <c r="W97" s="6" t="inlineStr"/>
+      <c r="V97" s="5" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="W97" s="6" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -6632,12 +6640,12 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>ADPPV2</t>
+          <t>CBWWPV2</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -6646,7 +6654,7 @@
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>0.2</v>
+        <v>1.08</v>
       </c>
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="5" t="inlineStr"/>
@@ -6654,9 +6662,7 @@
       <c r="H99" s="5" t="inlineStr"/>
       <c r="I99" s="5" t="inlineStr"/>
       <c r="J99" s="5" t="inlineStr"/>
-      <c r="K99" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="K99" s="5" t="inlineStr"/>
       <c r="L99" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6687,33 +6693,29 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>ADPPV1</t>
+          <t>CBWWDG2</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>24.75</v>
+        <v>0.72</v>
       </c>
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="5" t="inlineStr"/>
       <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr"/>
-      <c r="J100" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="K100" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="J100" s="5" t="inlineStr"/>
+      <c r="K100" s="5" t="inlineStr"/>
       <c r="L100" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6744,21 +6746,21 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1</t>
+          <t>CBWWPV1</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>7.76</v>
+        <v>2.75</v>
       </c>
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="5" t="inlineStr"/>
@@ -6767,57 +6769,51 @@
       <c r="I101" s="5" t="inlineStr"/>
       <c r="J101" s="5" t="inlineStr"/>
       <c r="K101" s="5" t="inlineStr"/>
-      <c r="L101" s="5" t="inlineStr"/>
-      <c r="M101" s="5" t="inlineStr"/>
+      <c r="L101" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="M101" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="N101" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O101" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="O101" s="5" t="inlineStr"/>
       <c r="P101" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q101" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="Q101" s="5" t="inlineStr"/>
       <c r="R101" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S101" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="S101" s="5" t="inlineStr"/>
       <c r="T101" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U101" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V101" s="5" t="n">
-        <v>-0.0004</v>
-      </c>
-      <c r="W101" s="6" t="n">
-        <v>-0.04</v>
-      </c>
+      <c r="V101" s="5" t="inlineStr"/>
+      <c r="W101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>ADPMH1</t>
+          <t>CBWWBG1</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>1.44</v>
+        <v>0.664</v>
       </c>
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="5" t="inlineStr"/>
@@ -6825,9 +6821,7 @@
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr"/>
-      <c r="K102" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="K102" s="5" t="inlineStr"/>
       <c r="L102" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6858,21 +6852,21 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>CBWWBG1</t>
+          <t>ADPBA1</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>0.664</v>
+        <v>7.76</v>
       </c>
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="5" t="inlineStr"/>
@@ -6881,32 +6875,38 @@
       <c r="I103" s="5" t="inlineStr"/>
       <c r="J103" s="5" t="inlineStr"/>
       <c r="K103" s="5" t="inlineStr"/>
-      <c r="L103" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="M103" s="5" t="n">
-        <v>1.0039</v>
-      </c>
+      <c r="L103" s="5" t="inlineStr"/>
+      <c r="M103" s="5" t="inlineStr"/>
       <c r="N103" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O103" s="5" t="inlineStr"/>
+      <c r="O103" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="P103" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q103" s="5" t="inlineStr"/>
+      <c r="Q103" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="R103" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S103" s="5" t="inlineStr"/>
+      <c r="S103" s="5" t="n">
+        <v>1.0033</v>
+      </c>
       <c r="T103" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U103" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V103" s="5" t="inlineStr"/>
-      <c r="W103" s="6" t="inlineStr"/>
+      <c r="V103" s="5" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="W103" s="6" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -7143,24 +7143,20 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>HIGHBRY1</t>
+          <t>AMCORGR</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Highbury Landfill Gas Power Station</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>Other Renewable</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>Amcor Glass, Gawler Plant</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="3" t="inlineStr"/>
       <c r="E108" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0111</v>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
       <c r="G108" s="5" t="inlineStr"/>
@@ -7184,24 +7180,24 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>STANV2</t>
+          <t>TEATREE1</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Pt Stanvac Power Station</t>
+          <t>Tea Tree Gully Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D109" s="4" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
       <c r="G109" s="5" t="inlineStr"/>
@@ -7266,12 +7262,12 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>ANGAS1</t>
+          <t>STANV2</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>ANGASTON POWER STATION</t>
+          <t>Pt Stanvac Power Station</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -7280,10 +7276,10 @@
         </is>
       </c>
       <c r="D111" s="4" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1.0061</v>
+        <v>1.0075</v>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
       <c r="G111" s="5" t="inlineStr"/>
@@ -7307,20 +7303,24 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>AMCORGR</t>
+          <t>HIGHBRY1</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Amcor Glass, Gawler Plant</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D112" s="3" t="inlineStr"/>
+          <t>Highbury Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="E112" s="5" t="n">
-        <v>1.0111</v>
+        <v>1.0042</v>
       </c>
       <c r="F112" s="5" t="inlineStr"/>
       <c r="G112" s="5" t="inlineStr"/>
@@ -7344,7 +7344,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>ANGAS2</t>
+          <t>ANGAS1</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E113" s="5" t="n">
         <v>1.0061</v>
@@ -7385,24 +7385,24 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>TEATREE1</t>
+          <t>ANGAS2</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Tea Tree Gully Landfill Gas Power Station</t>
+          <t>ANGASTON POWER STATION</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0061</v>
       </c>
       <c r="F114" s="5" t="inlineStr"/>
       <c r="G114" s="5" t="inlineStr"/>
@@ -7426,20 +7426,24 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>PLAYB-AG</t>
+          <t>NPS1</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Playford B Power Station</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="3" t="inlineStr"/>
+          <t>NORTHERN POWER STATION</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>265</v>
+      </c>
       <c r="E115" s="5" t="n">
-        <v>0.9881</v>
+        <v>0.9826</v>
       </c>
       <c r="F115" s="5" t="n">
         <v>1.0098</v>
@@ -7508,7 +7512,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>NPSNL1</t>
+          <t>NPS2</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -7522,13 +7526,13 @@
         </is>
       </c>
       <c r="D117" s="4" t="n">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9826</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>1.0132</v>
+        <v>1.0098</v>
       </c>
       <c r="G117" s="5" t="inlineStr"/>
       <c r="H117" s="5" t="inlineStr"/>
@@ -7551,7 +7555,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>NPS2</t>
+          <t>NPSNL1</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -7565,13 +7569,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0.9826</v>
+        <v>0.9929</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0132</v>
       </c>
       <c r="G118" s="5" t="inlineStr"/>
       <c r="H118" s="5" t="inlineStr"/>
@@ -7594,24 +7598,20 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>NPS1</t>
+          <t>PLAYB-AG</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>NORTHERN POWER STATION</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>265</v>
-      </c>
+          <t>Playford B Power Station</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="3" t="inlineStr"/>
       <c r="E119" s="5" t="n">
-        <v>0.9826</v>
+        <v>0.9881</v>
       </c>
       <c r="F119" s="5" t="n">
         <v>1.0098</v>
@@ -7637,30 +7637,30 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>BLULAKE1</t>
+          <t>TERMSTOR</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Blue Lake Milling Power Plant</t>
+          <t>Terminal Storage Mini Hydro Power Station</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1.0062</v>
+        <v>1.0042</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.9703000000000001</v>
+        <v>1.0037</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.978</v>
+        <v>1.0034</v>
       </c>
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr"/>
@@ -7682,30 +7682,30 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>PEDLER1</t>
+          <t>BLULAKE1</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Pedler Creek Landfill Gas Power Station Units 1-3</t>
+          <t>Blue Lake Milling Power Plant</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D121" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0062</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>1.0051</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>1.0047</v>
+        <v>0.978</v>
       </c>
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr"/>
@@ -7727,30 +7727,30 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>TERMSTOR</t>
+          <t>PEDLER1</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Terminal Storage Mini Hydro Power Station</t>
+          <t>Pedler Creek Landfill Gas Power Station Units 1-3</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>1.0037</v>
+        <v>1.0051</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>1.0034</v>
+        <v>1.0047</v>
       </c>
       <c r="H122" s="5" t="inlineStr"/>
       <c r="I122" s="5" t="inlineStr"/>
@@ -7982,33 +7982,41 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>TB2BG1</t>
+          <t>ADPBA1G</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Tailem Bend 2 Hybrid Renewable Power Station</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="3" t="inlineStr"/>
+          <t>Adelaide Desalination Plant</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="5" t="inlineStr"/>
       <c r="G127" s="5" t="inlineStr"/>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr"/>
-      <c r="J127" s="5" t="inlineStr"/>
-      <c r="K127" s="5" t="inlineStr"/>
+      <c r="J127" s="5" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L127" s="5" t="n">
-        <v>0.9966</v>
+        <v>1.0036</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0039</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>1.0102</v>
+        <v>1.0025</v>
       </c>
       <c r="O127" s="5" t="inlineStr"/>
       <c r="P127" s="5" t="inlineStr"/>
@@ -8023,12 +8031,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>TIBG1</t>
+          <t>BOWWBA1G</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Torrens Island BESS</t>
+          <t>Bolivar Waste Water Treatment Plant</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -8037,7 +8045,7 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="5" t="inlineStr"/>
@@ -8045,15 +8053,17 @@
       <c r="H128" s="5" t="inlineStr"/>
       <c r="I128" s="5" t="inlineStr"/>
       <c r="J128" s="5" t="inlineStr"/>
-      <c r="K128" s="5" t="inlineStr"/>
+      <c r="K128" s="5" t="n">
+        <v>1.0011</v>
+      </c>
       <c r="L128" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0002</v>
       </c>
       <c r="M128" s="5" t="n">
-        <v>0.9996</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>0.9998</v>
+        <v>1.0004</v>
       </c>
       <c r="O128" s="5" t="inlineStr"/>
       <c r="P128" s="5" t="inlineStr"/>
@@ -8068,12 +8078,12 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>BOWWBA1G</t>
+          <t>DALNTH01</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Bolivar Waste Water Treatment Plant</t>
+          <t>Dalrymple North BESS</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -8082,25 +8092,33 @@
         </is>
       </c>
       <c r="D129" s="4" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E129" s="5" t="inlineStr"/>
       <c r="F129" s="5" t="inlineStr"/>
-      <c r="G129" s="5" t="inlineStr"/>
-      <c r="H129" s="5" t="inlineStr"/>
-      <c r="I129" s="5" t="inlineStr"/>
-      <c r="J129" s="5" t="inlineStr"/>
+      <c r="G129" s="5" t="n">
+        <v>0.8848</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>0.9045</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>0.9193</v>
+      </c>
       <c r="K129" s="5" t="n">
-        <v>1.0011</v>
+        <v>0.9212</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>1.0002</v>
+        <v>0.9432</v>
       </c>
       <c r="M129" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.8954</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>1.0004</v>
+        <v>0.9092</v>
       </c>
       <c r="O129" s="5" t="inlineStr"/>
       <c r="P129" s="5" t="inlineStr"/>
@@ -8115,12 +8133,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>LBBG1</t>
+          <t>CBWWBA1G</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney BESS1</t>
+          <t>Christies Beach WWTP</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -8129,29 +8147,23 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="5" t="inlineStr"/>
       <c r="G130" s="5" t="inlineStr"/>
       <c r="H130" s="5" t="inlineStr"/>
-      <c r="I130" s="5" t="n">
-        <v>0.9922</v>
-      </c>
-      <c r="J130" s="5" t="n">
-        <v>0.9741</v>
-      </c>
-      <c r="K130" s="5" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="I130" s="5" t="inlineStr"/>
+      <c r="J130" s="5" t="inlineStr"/>
+      <c r="K130" s="5" t="inlineStr"/>
       <c r="L130" s="5" t="n">
-        <v>0.9851</v>
+        <v>1.0036</v>
       </c>
       <c r="M130" s="5" t="n">
-        <v>0.979</v>
+        <v>1.0039</v>
       </c>
       <c r="N130" s="5" t="n">
-        <v>0.9841</v>
+        <v>1.0025</v>
       </c>
       <c r="O130" s="5" t="inlineStr"/>
       <c r="P130" s="5" t="inlineStr"/>
@@ -8213,12 +8225,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1G</t>
+          <t>HPRG1</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach WWTP</t>
+          <t>Hornsdale Power Reserve</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -8227,23 +8239,33 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="E132" s="5" t="inlineStr"/>
       <c r="F132" s="5" t="inlineStr"/>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="5" t="inlineStr"/>
-      <c r="I132" s="5" t="inlineStr"/>
-      <c r="J132" s="5" t="inlineStr"/>
-      <c r="K132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>0.9772</v>
+      </c>
       <c r="L132" s="5" t="n">
-        <v>1.0036</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>1.0039</v>
+        <v>0.9653</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>1.0025</v>
+        <v>0.9657</v>
       </c>
       <c r="O132" s="5" t="inlineStr"/>
       <c r="P132" s="5" t="inlineStr"/>
@@ -8258,47 +8280,33 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>HPRG1</t>
+          <t>TB2BG1</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Power Reserve</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="n">
-        <v>150</v>
-      </c>
+          <t>Tailem Bend 2 Hybrid Renewable Power Station</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D133" s="3" t="inlineStr"/>
       <c r="E133" s="5" t="inlineStr"/>
       <c r="F133" s="5" t="inlineStr"/>
-      <c r="G133" s="5" t="n">
-        <v>0.9848</v>
-      </c>
-      <c r="H133" s="5" t="n">
-        <v>0.9771</v>
-      </c>
-      <c r="I133" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="J133" s="5" t="n">
-        <v>0.9838</v>
-      </c>
-      <c r="K133" s="5" t="n">
-        <v>0.9772</v>
-      </c>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr"/>
+      <c r="I133" s="5" t="inlineStr"/>
+      <c r="J133" s="5" t="inlineStr"/>
+      <c r="K133" s="5" t="inlineStr"/>
       <c r="L133" s="5" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9966</v>
       </c>
       <c r="M133" s="5" t="n">
-        <v>0.9653</v>
+        <v>1.0079</v>
       </c>
       <c r="N133" s="5" t="n">
-        <v>0.9657</v>
+        <v>1.0102</v>
       </c>
       <c r="O133" s="5" t="inlineStr"/>
       <c r="P133" s="5" t="inlineStr"/>
@@ -8313,12 +8321,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>DALNTH01</t>
+          <t>TIBG1</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Dalrymple North BESS</t>
+          <t>Torrens Island BESS</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -8327,33 +8335,23 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="5" t="inlineStr"/>
-      <c r="G134" s="5" t="n">
-        <v>0.8848</v>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="I134" s="5" t="n">
-        <v>0.9045</v>
-      </c>
-      <c r="J134" s="5" t="n">
-        <v>0.9193</v>
-      </c>
-      <c r="K134" s="5" t="n">
-        <v>0.9212</v>
-      </c>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr"/>
+      <c r="I134" s="5" t="inlineStr"/>
+      <c r="J134" s="5" t="inlineStr"/>
+      <c r="K134" s="5" t="inlineStr"/>
       <c r="L134" s="5" t="n">
-        <v>0.9432</v>
+        <v>1.0001</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.8954</v>
+        <v>0.9996</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>0.9092</v>
+        <v>0.9998</v>
       </c>
       <c r="O134" s="5" t="inlineStr"/>
       <c r="P134" s="5" t="inlineStr"/>
@@ -8368,12 +8366,12 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1G</t>
+          <t>LBBG1</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Lake Bonney BESS1</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -8382,27 +8380,29 @@
         </is>
       </c>
       <c r="D135" s="4" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E135" s="5" t="inlineStr"/>
       <c r="F135" s="5" t="inlineStr"/>
       <c r="G135" s="5" t="inlineStr"/>
       <c r="H135" s="5" t="inlineStr"/>
-      <c r="I135" s="5" t="inlineStr"/>
+      <c r="I135" s="5" t="n">
+        <v>0.9922</v>
+      </c>
       <c r="J135" s="5" t="n">
-        <v>1.0038</v>
+        <v>0.9741</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>1.0055</v>
+        <v>1.0022</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>1.0036</v>
+        <v>0.9851</v>
       </c>
       <c r="M135" s="5" t="n">
-        <v>1.0039</v>
+        <v>0.979</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>1.0025</v>
+        <v>0.9841</v>
       </c>
       <c r="O135" s="5" t="inlineStr"/>
       <c r="P135" s="5" t="inlineStr"/>
@@ -8779,7 +8779,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -8871,7 +8871,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -8963,12 +8963,14 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>HDWF2</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr"/>
+          <t>HDWF1</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0.9792999999999999</v>
+      </c>
       <c r="C12" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0.9841</v>
@@ -9007,14 +9009,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HDWF1</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>0.9792999999999999</v>
-      </c>
+          <t>HDWF2</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9918</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0.9841</v>
@@ -9131,7 +9131,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>BLUFF1</t>
+          <t>NBHWF1</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -9177,7 +9177,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>NBHWF1</t>
+          <t>BLUFF1</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -9223,7 +9223,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>SNUG2</t>
+          <t>SNUG3</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -9269,7 +9269,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>SNUG3</t>
+          <t>SNUG2</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -9539,7 +9539,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>AGLHAL</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
@@ -9585,7 +9585,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>AGLHAL</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -9729,72 +9729,72 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>LGAPWF1</t>
+          <t>LGAPBS1</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>0.9947</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0.9821</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.9779</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>0.9628</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0.9601</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0.9576</v>
-      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="n">
         <v>0.9689</v>
       </c>
-      <c r="N30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="n">
+        <v>0.9689</v>
+      </c>
       <c r="O30" s="5" t="n">
         <v>0.9661</v>
       </c>
-      <c r="P30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="n">
+        <v>0.9661</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>LGAPBS1</t>
+          <t>LGAPWF1</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="n">
+        <v>0.9947</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.9821</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.9628</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0.9601</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.9576</v>
+      </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="n">
         <v>0.9689</v>
       </c>
-      <c r="N31" s="5" t="n">
-        <v>0.9689</v>
-      </c>
+      <c r="N31" s="5" t="inlineStr"/>
       <c r="O31" s="5" t="n">
         <v>0.9661</v>
       </c>
-      <c r="P31" s="5" t="n">
-        <v>0.9661</v>
-      </c>
+      <c r="P31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -9929,7 +9929,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -9975,7 +9975,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -10021,14 +10021,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>BNGSF1</t>
+          <t>BNGSF2</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr"/>
       <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="n">
-        <v>0.9946</v>
-      </c>
+      <c r="D38" s="5" t="inlineStr"/>
       <c r="E38" s="5" t="n">
         <v>0.97</v>
       </c>
@@ -10063,12 +10061,14 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>BNGSF2</t>
+          <t>BNGSF1</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr"/>
       <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="n">
+        <v>0.9946</v>
+      </c>
       <c r="E39" s="5" t="n">
         <v>0.97</v>
       </c>
@@ -10413,7 +10413,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -10459,7 +10459,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -10585,7 +10585,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>QPS1</t>
+          <t>QPS5</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -10631,7 +10631,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>QPS2</t>
+          <t>QPS3</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
@@ -10677,7 +10677,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>QPS3</t>
+          <t>QPS4</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
@@ -10723,7 +10723,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>QPS4</t>
+          <t>QPS2</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
@@ -10769,7 +10769,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>QPS5</t>
+          <t>QPS1</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
@@ -10891,7 +10891,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr"/>
@@ -10901,31 +10901,29 @@
       <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
+      <c r="I59" s="5" t="n">
+        <v>0.9687</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>1.0079</v>
+      </c>
       <c r="K59" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="L59" s="5" t="n">
-        <v>1.0102</v>
-      </c>
+      <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="N59" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+      <c r="N59" s="5" t="inlineStr"/>
       <c r="O59" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="P59" s="5" t="n">
-        <v>0.9968</v>
-      </c>
+      <c r="P59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr"/>
@@ -10935,24 +10933,26 @@
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="5" t="n">
-        <v>0.9687</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>1.0079</v>
-      </c>
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="L60" s="5" t="inlineStr"/>
+      <c r="L60" s="5" t="n">
+        <v>1.0102</v>
+      </c>
       <c r="M60" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="N60" s="5" t="inlineStr"/>
+      <c r="N60" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="O60" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="P60" s="5" t="inlineStr"/>
+      <c r="P60" s="5" t="n">
+        <v>0.9968</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -10997,7 +10997,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT3</t>
+          <t>DRYCGT2</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -11043,7 +11043,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT2</t>
+          <t>DRYCGT3</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
@@ -11215,7 +11215,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>TORRB1</t>
+          <t>TORRB4</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -11261,7 +11261,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>TORRB2</t>
+          <t>TORRB1</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
@@ -11353,7 +11353,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>TORRB4</t>
+          <t>TORRB2</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
@@ -11399,82 +11399,82 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>TIB1</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr"/>
-      <c r="C71" s="5" t="inlineStr"/>
-      <c r="D71" s="5" t="inlineStr"/>
-      <c r="E71" s="5" t="inlineStr"/>
-      <c r="F71" s="5" t="inlineStr"/>
-      <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="5" t="inlineStr"/>
+          <t>OSB-AG</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>0.9992</v>
+      </c>
       <c r="K71" s="5" t="n">
-        <v>0.9996</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>0.9998</v>
-      </c>
+        <v>0.9994</v>
+      </c>
+      <c r="L71" s="5" t="inlineStr"/>
       <c r="M71" s="5" t="n">
-        <v>0.9993</v>
-      </c>
-      <c r="N71" s="5" t="n">
-        <v>0.9992</v>
-      </c>
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="N71" s="5" t="inlineStr"/>
       <c r="O71" s="5" t="n">
         <v>0.9997</v>
       </c>
-      <c r="P71" s="5" t="n">
-        <v>0.9994</v>
-      </c>
+      <c r="P71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>OSB-AG</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>0.9994</v>
-      </c>
-      <c r="D72" s="5" t="n">
-        <v>0.9988</v>
-      </c>
-      <c r="E72" s="5" t="n">
+          <t>TIB1</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr"/>
+      <c r="C72" s="5" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="N72" s="5" t="n">
         <v>0.9992</v>
       </c>
-      <c r="F72" s="5" t="n">
-        <v>0.9997</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>0.9998</v>
-      </c>
-      <c r="H72" s="5" t="n">
-        <v>0.9999</v>
-      </c>
-      <c r="I72" s="5" t="n">
-        <v>0.9999</v>
-      </c>
-      <c r="J72" s="5" t="n">
-        <v>0.9992</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>0.9994</v>
-      </c>
-      <c r="L72" s="5" t="inlineStr"/>
-      <c r="M72" s="5" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="N72" s="5" t="inlineStr"/>
       <c r="O72" s="5" t="n">
         <v>0.9997</v>
       </c>
-      <c r="P72" s="5" t="inlineStr"/>
+      <c r="P72" s="5" t="n">
+        <v>0.9994</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -11513,34 +11513,42 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>BARKIPS1</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr"/>
-      <c r="C74" s="5" t="inlineStr"/>
-      <c r="D74" s="5" t="inlineStr"/>
-      <c r="E74" s="5" t="inlineStr"/>
+          <t>DG_SA1</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="F74" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="J74" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="L74" s="5" t="inlineStr"/>
       <c r="M74" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
       <c r="O74" s="5" t="n">
@@ -11551,42 +11559,34 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>TORNL1</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>BARKIPS1</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr"/>
+      <c r="C75" s="5" t="inlineStr"/>
+      <c r="D75" s="5" t="inlineStr"/>
+      <c r="E75" s="5" t="inlineStr"/>
       <c r="F75" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="J75" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="L75" s="5" t="inlineStr"/>
       <c r="M75" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
       <c r="O75" s="5" t="n">
@@ -11597,7 +11597,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>DG_SA1</t>
+          <t>TORNL1</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
@@ -11643,27 +11643,15 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>BOLIVAR1</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>1.0054</v>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>1.0012</v>
-      </c>
+          <t>BOWWDG1</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr"/>
+      <c r="C77" s="5" t="inlineStr"/>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
       <c r="H77" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -11723,15 +11711,27 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>BOWWDG1</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr"/>
-      <c r="C79" s="5" t="inlineStr"/>
-      <c r="D79" s="5" t="inlineStr"/>
-      <c r="E79" s="5" t="inlineStr"/>
-      <c r="F79" s="5" t="inlineStr"/>
-      <c r="G79" s="5" t="inlineStr"/>
+          <t>BOLIVAR1</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>1.0045</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>1.0012</v>
+      </c>
       <c r="H79" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -12029,7 +12029,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>HVWWPV1</t>
+          <t>HVWWBA1</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr"/>
@@ -12038,32 +12038,32 @@
       <c r="E87" s="5" t="inlineStr"/>
       <c r="F87" s="5" t="inlineStr"/>
       <c r="G87" s="5" t="inlineStr"/>
-      <c r="H87" s="5" t="n">
-        <v>1.0052</v>
-      </c>
-      <c r="I87" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="J87" s="5" t="n">
-        <v>1.0041</v>
-      </c>
+      <c r="H87" s="5" t="inlineStr"/>
+      <c r="I87" s="5" t="inlineStr"/>
+      <c r="J87" s="5" t="inlineStr"/>
       <c r="K87" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="L87" s="5" t="inlineStr"/>
+      <c r="L87" s="5" t="n">
+        <v>1.0043</v>
+      </c>
       <c r="M87" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="N87" s="5" t="inlineStr"/>
+      <c r="N87" s="5" t="n">
+        <v>1.0024</v>
+      </c>
       <c r="O87" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="P87" s="5" t="inlineStr"/>
+      <c r="P87" s="5" t="n">
+        <v>1.0022</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>HVWWBA1</t>
+          <t>HVWWPV1</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr"/>
@@ -12072,27 +12072,27 @@
       <c r="E88" s="5" t="inlineStr"/>
       <c r="F88" s="5" t="inlineStr"/>
       <c r="G88" s="5" t="inlineStr"/>
-      <c r="H88" s="5" t="inlineStr"/>
-      <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="5" t="inlineStr"/>
+      <c r="H88" s="5" t="n">
+        <v>1.0052</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>1.0041</v>
+      </c>
       <c r="K88" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="L88" s="5" t="n">
-        <v>1.0043</v>
-      </c>
+      <c r="L88" s="5" t="inlineStr"/>
       <c r="M88" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="N88" s="5" t="n">
-        <v>1.0024</v>
-      </c>
+      <c r="N88" s="5" t="inlineStr"/>
       <c r="O88" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="P88" s="5" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="P88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -12143,27 +12143,15 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>PTSTAN1</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C90" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D90" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>1.005</v>
-      </c>
+          <t>ADPPV2</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr"/>
+      <c r="C90" s="5" t="inlineStr"/>
+      <c r="D90" s="5" t="inlineStr"/>
+      <c r="E90" s="5" t="inlineStr"/>
+      <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="5" t="inlineStr"/>
       <c r="H90" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -12189,27 +12177,15 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C91" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D91" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>1.005</v>
-      </c>
+          <t>ADPPV3</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr"/>
+      <c r="C91" s="5" t="inlineStr"/>
+      <c r="D91" s="5" t="inlineStr"/>
+      <c r="E91" s="5" t="inlineStr"/>
+      <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -12235,26 +12211,16 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>LONSDALE</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C92" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D92" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>1.0053</v>
-      </c>
+          <t>ADPPV1</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr"/>
+      <c r="C92" s="5" t="inlineStr"/>
+      <c r="D92" s="5" t="inlineStr"/>
+      <c r="E92" s="5" t="inlineStr"/>
+      <c r="F92" s="5" t="inlineStr"/>
       <c r="G92" s="5" t="n">
-        <v>1.005</v>
+        <v>1.0038</v>
       </c>
       <c r="H92" s="5" t="n">
         <v>1.0055</v>
@@ -12281,7 +12247,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1</t>
+          <t>ADPMH1</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr"/>
@@ -12290,41 +12256,55 @@
       <c r="E93" s="5" t="inlineStr"/>
       <c r="F93" s="5" t="inlineStr"/>
       <c r="G93" s="5" t="inlineStr"/>
-      <c r="H93" s="5" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr"/>
-      <c r="J93" s="5" t="inlineStr"/>
+      <c r="H93" s="5" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="K93" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L93" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="L93" s="5" t="inlineStr"/>
       <c r="M93" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N93" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="N93" s="5" t="inlineStr"/>
       <c r="O93" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P93" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="P93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG2</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr"/>
-      <c r="C94" s="5" t="inlineStr"/>
-      <c r="D94" s="5" t="inlineStr"/>
-      <c r="E94" s="5" t="inlineStr"/>
-      <c r="F94" s="5" t="inlineStr"/>
-      <c r="G94" s="5" t="inlineStr"/>
-      <c r="H94" s="5" t="inlineStr"/>
+          <t>LONSDALE</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I94" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12347,16 +12327,30 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV1</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr"/>
-      <c r="C95" s="5" t="inlineStr"/>
-      <c r="D95" s="5" t="inlineStr"/>
-      <c r="E95" s="5" t="inlineStr"/>
-      <c r="F95" s="5" t="inlineStr"/>
-      <c r="G95" s="5" t="inlineStr"/>
-      <c r="H95" s="5" t="inlineStr"/>
+          <t>PTSTAN1</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I95" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12379,16 +12373,30 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV2</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr"/>
-      <c r="C96" s="5" t="inlineStr"/>
-      <c r="D96" s="5" t="inlineStr"/>
-      <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="5" t="inlineStr"/>
-      <c r="G96" s="5" t="inlineStr"/>
-      <c r="H96" s="5" t="inlineStr"/>
+          <t>STARHLWF</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I96" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12411,7 +12419,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>ADPPV3</t>
+          <t>CBWWBA1</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr"/>
@@ -12420,27 +12428,27 @@
       <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="5" t="inlineStr"/>
       <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="I97" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="J97" s="5" t="n">
-        <v>1.0039</v>
-      </c>
+      <c r="H97" s="5" t="inlineStr"/>
+      <c r="I97" s="5" t="inlineStr"/>
+      <c r="J97" s="5" t="inlineStr"/>
       <c r="K97" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L97" s="5" t="inlineStr"/>
+      <c r="L97" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="M97" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N97" s="5" t="inlineStr"/>
+      <c r="N97" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="O97" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P97" s="5" t="inlineStr"/>
+      <c r="P97" s="5" t="n">
+        <v>1.0033</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -12477,7 +12485,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>ADPPV2</t>
+          <t>CBWWPV2</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr"/>
@@ -12486,9 +12494,7 @@
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="5" t="inlineStr"/>
       <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="H99" s="5" t="inlineStr"/>
       <c r="I99" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12511,7 +12517,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>ADPPV1</t>
+          <t>CBWWDG2</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr"/>
@@ -12519,12 +12525,8 @@
       <c r="D100" s="5" t="inlineStr"/>
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="5" t="inlineStr"/>
-      <c r="G100" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12547,7 +12549,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1</t>
+          <t>CBWWPV1</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr"/>
@@ -12557,31 +12559,29 @@
       <c r="F101" s="5" t="inlineStr"/>
       <c r="G101" s="5" t="inlineStr"/>
       <c r="H101" s="5" t="inlineStr"/>
-      <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="5" t="inlineStr"/>
+      <c r="I101" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="K101" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L101" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="L101" s="5" t="inlineStr"/>
       <c r="M101" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N101" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="N101" s="5" t="inlineStr"/>
       <c r="O101" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P101" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="P101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>ADPMH1</t>
+          <t>CBWWBG1</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr"/>
@@ -12590,9 +12590,7 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="5" t="inlineStr"/>
       <c r="G102" s="5" t="inlineStr"/>
-      <c r="H102" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12615,7 +12613,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>CBWWBG1</t>
+          <t>ADPBA1</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr"/>
@@ -12625,24 +12623,26 @@
       <c r="F103" s="5" t="inlineStr"/>
       <c r="G103" s="5" t="inlineStr"/>
       <c r="H103" s="5" t="inlineStr"/>
-      <c r="I103" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="J103" s="5" t="n">
-        <v>1.0039</v>
-      </c>
+      <c r="I103" s="5" t="inlineStr"/>
+      <c r="J103" s="5" t="inlineStr"/>
       <c r="K103" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L103" s="5" t="inlineStr"/>
+      <c r="L103" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="M103" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N103" s="5" t="inlineStr"/>
+      <c r="N103" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="O103" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P103" s="5" t="inlineStr"/>
+      <c r="P103" s="5" t="n">
+        <v>1.0033</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -12795,11 +12795,11 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>HIGHBRY1</t>
+          <t>AMCORGR</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0111</v>
       </c>
       <c r="C108" s="5" t="inlineStr"/>
       <c r="D108" s="5" t="inlineStr"/>
@@ -12819,11 +12819,11 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>STANV2</t>
+          <t>TEATREE1</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="C109" s="5" t="inlineStr"/>
       <c r="D109" s="5" t="inlineStr"/>
@@ -12867,11 +12867,11 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>ANGAS1</t>
+          <t>STANV2</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
-        <v>1.0061</v>
+        <v>1.0075</v>
       </c>
       <c r="C111" s="5" t="inlineStr"/>
       <c r="D111" s="5" t="inlineStr"/>
@@ -12891,11 +12891,11 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>AMCORGR</t>
+          <t>HIGHBRY1</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
-        <v>1.0111</v>
+        <v>1.0042</v>
       </c>
       <c r="C112" s="5" t="inlineStr"/>
       <c r="D112" s="5" t="inlineStr"/>
@@ -12915,7 +12915,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>ANGAS2</t>
+          <t>ANGAS1</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -12939,11 +12939,11 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>TEATREE1</t>
+          <t>ANGAS2</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0061</v>
       </c>
       <c r="C114" s="5" t="inlineStr"/>
       <c r="D114" s="5" t="inlineStr"/>
@@ -12963,11 +12963,11 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>PLAYB-AG</t>
+          <t>NPS1</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>0.9881</v>
+        <v>0.9826</v>
       </c>
       <c r="C115" s="5" t="n">
         <v>1.0098</v>
@@ -13015,14 +13015,14 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>NPSNL1</t>
+          <t>NPS2</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9826</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1.0132</v>
+        <v>1.0098</v>
       </c>
       <c r="D117" s="5" t="inlineStr"/>
       <c r="E117" s="5" t="inlineStr"/>
@@ -13041,14 +13041,14 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>NPS2</t>
+          <t>NPSNL1</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
-        <v>0.9826</v>
+        <v>0.9929</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0132</v>
       </c>
       <c r="D118" s="5" t="inlineStr"/>
       <c r="E118" s="5" t="inlineStr"/>
@@ -13067,11 +13067,11 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>NPS1</t>
+          <t>PLAYB-AG</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>0.9826</v>
+        <v>0.9881</v>
       </c>
       <c r="C119" s="5" t="n">
         <v>1.0098</v>
@@ -13093,17 +13093,17 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>BLULAKE1</t>
+          <t>TERMSTOR</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>1.0062</v>
+        <v>1.0042</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>0.9703000000000001</v>
+        <v>1.0037</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>0.978</v>
+        <v>1.0034</v>
       </c>
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="5" t="inlineStr"/>
@@ -13121,17 +13121,17 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>PEDLER1</t>
+          <t>BLULAKE1</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0062</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>1.0051</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>1.0047</v>
+        <v>0.978</v>
       </c>
       <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="5" t="inlineStr"/>
@@ -13149,17 +13149,17 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>TERMSTOR</t>
+          <t>PEDLER1</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>1.0037</v>
+        <v>1.0051</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>1.0034</v>
+        <v>1.0047</v>
       </c>
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="5" t="inlineStr"/>
@@ -13319,7 +13319,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>TB2BG1</t>
+          <t>ADPBA1G</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr"/>
@@ -13327,16 +13327,20 @@
       <c r="D127" s="5" t="inlineStr"/>
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="5" t="inlineStr"/>
-      <c r="G127" s="5" t="inlineStr"/>
-      <c r="H127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I127" s="5" t="n">
-        <v>0.9966</v>
+        <v>1.0036</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0039</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>1.0102</v>
+        <v>1.0025</v>
       </c>
       <c r="L127" s="5" t="inlineStr"/>
       <c r="M127" s="5" t="inlineStr"/>
@@ -13347,7 +13351,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>TIBG1</t>
+          <t>BOWWBA1G</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr"/>
@@ -13356,15 +13360,17 @@
       <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="5" t="inlineStr"/>
       <c r="G128" s="5" t="inlineStr"/>
-      <c r="H128" s="5" t="inlineStr"/>
+      <c r="H128" s="5" t="n">
+        <v>1.0011</v>
+      </c>
       <c r="I128" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0002</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>0.9996</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>0.9998</v>
+        <v>1.0004</v>
       </c>
       <c r="L128" s="5" t="inlineStr"/>
       <c r="M128" s="5" t="inlineStr"/>
@@ -13375,26 +13381,34 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>BOWWBA1G</t>
+          <t>DALNTH01</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr"/>
       <c r="C129" s="5" t="inlineStr"/>
-      <c r="D129" s="5" t="inlineStr"/>
-      <c r="E129" s="5" t="inlineStr"/>
-      <c r="F129" s="5" t="inlineStr"/>
-      <c r="G129" s="5" t="inlineStr"/>
+      <c r="D129" s="5" t="n">
+        <v>0.8848</v>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>0.9045</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.9193</v>
+      </c>
       <c r="H129" s="5" t="n">
-        <v>1.0011</v>
+        <v>0.9212</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>1.0002</v>
+        <v>0.9432</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.8954</v>
       </c>
       <c r="K129" s="5" t="n">
-        <v>1.0004</v>
+        <v>0.9092</v>
       </c>
       <c r="L129" s="5" t="inlineStr"/>
       <c r="M129" s="5" t="inlineStr"/>
@@ -13405,30 +13419,24 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>LBBG1</t>
+          <t>CBWWBA1G</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr"/>
       <c r="C130" s="5" t="inlineStr"/>
       <c r="D130" s="5" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr"/>
-      <c r="F130" s="5" t="n">
-        <v>0.9922</v>
-      </c>
-      <c r="G130" s="5" t="n">
-        <v>0.9741</v>
-      </c>
-      <c r="H130" s="5" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="F130" s="5" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr"/>
+      <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="n">
-        <v>0.9851</v>
+        <v>1.0036</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>0.979</v>
+        <v>1.0039</v>
       </c>
       <c r="K130" s="5" t="n">
-        <v>0.9841</v>
+        <v>1.0025</v>
       </c>
       <c r="L130" s="5" t="inlineStr"/>
       <c r="M130" s="5" t="inlineStr"/>
@@ -13469,24 +13477,34 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1G</t>
+          <t>HPRG1</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr"/>
       <c r="C132" s="5" t="inlineStr"/>
-      <c r="D132" s="5" t="inlineStr"/>
-      <c r="E132" s="5" t="inlineStr"/>
-      <c r="F132" s="5" t="inlineStr"/>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="5" t="inlineStr"/>
+      <c r="D132" s="5" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>0.9772</v>
+      </c>
       <c r="I132" s="5" t="n">
-        <v>1.0036</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>1.0039</v>
+        <v>0.9653</v>
       </c>
       <c r="K132" s="5" t="n">
-        <v>1.0025</v>
+        <v>0.9657</v>
       </c>
       <c r="L132" s="5" t="inlineStr"/>
       <c r="M132" s="5" t="inlineStr"/>
@@ -13497,34 +13515,24 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>HPRG1</t>
+          <t>TB2BG1</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr"/>
       <c r="C133" s="5" t="inlineStr"/>
-      <c r="D133" s="5" t="n">
-        <v>0.9848</v>
-      </c>
-      <c r="E133" s="5" t="n">
-        <v>0.9771</v>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="G133" s="5" t="n">
-        <v>0.9838</v>
-      </c>
-      <c r="H133" s="5" t="n">
-        <v>0.9772</v>
-      </c>
+      <c r="D133" s="5" t="inlineStr"/>
+      <c r="E133" s="5" t="inlineStr"/>
+      <c r="F133" s="5" t="inlineStr"/>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9966</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>0.9653</v>
+        <v>1.0079</v>
       </c>
       <c r="K133" s="5" t="n">
-        <v>0.9657</v>
+        <v>1.0102</v>
       </c>
       <c r="L133" s="5" t="inlineStr"/>
       <c r="M133" s="5" t="inlineStr"/>
@@ -13535,34 +13543,24 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>DALNTH01</t>
+          <t>TIBG1</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr"/>
       <c r="C134" s="5" t="inlineStr"/>
-      <c r="D134" s="5" t="n">
-        <v>0.8848</v>
-      </c>
-      <c r="E134" s="5" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>0.9045</v>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>0.9193</v>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>0.9212</v>
-      </c>
+      <c r="D134" s="5" t="inlineStr"/>
+      <c r="E134" s="5" t="inlineStr"/>
+      <c r="F134" s="5" t="inlineStr"/>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="n">
-        <v>0.9432</v>
+        <v>1.0001</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>0.8954</v>
+        <v>0.9996</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>0.9092</v>
+        <v>0.9998</v>
       </c>
       <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="5" t="inlineStr"/>
@@ -13573,28 +13571,30 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1G</t>
+          <t>LBBG1</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr"/>
       <c r="C135" s="5" t="inlineStr"/>
       <c r="D135" s="5" t="inlineStr"/>
       <c r="E135" s="5" t="inlineStr"/>
-      <c r="F135" s="5" t="inlineStr"/>
+      <c r="F135" s="5" t="n">
+        <v>0.9922</v>
+      </c>
       <c r="G135" s="5" t="n">
-        <v>1.0038</v>
+        <v>0.9741</v>
       </c>
       <c r="H135" s="5" t="n">
-        <v>1.0055</v>
+        <v>1.0022</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>1.0036</v>
+        <v>0.9851</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>1.0039</v>
+        <v>0.979</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>1.0025</v>
+        <v>0.9841</v>
       </c>
       <c r="L135" s="5" t="inlineStr"/>
       <c r="M135" s="5" t="inlineStr"/>
@@ -14345,17 +14345,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>AGLHAL</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Hallett Power Station</t>
+          <t>Hallett 1 Wind Farm</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -14374,17 +14374,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>AGLHAL</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Hallett 1 Wind Farm</t>
+          <t>Hallett Power Station</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -14476,7 +14476,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -14505,7 +14505,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -14592,12 +14592,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 3 Wind Farm</t>
+          <t>Lake Bonney Wind Farm Stage 1</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -14650,12 +14650,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Wind Farm Stage 1</t>
+          <t>Lake Bonney Stage 3 Wind Farm</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -14766,7 +14766,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -14795,7 +14795,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -14805,7 +14805,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -14969,12 +14969,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Snowtown South Wind Farm</t>
+          <t>Snowtown Wind Farm Stage 2 North</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -14998,12 +14998,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Snowtown Wind Farm Stage 2 North</t>
+          <t>Snowtown South Wind Farm</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -15027,7 +15027,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TORRB3</t>
+          <t>TORRB4</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
